--- a/LBO_Complex_Template_IRR_MoM.xlsx
+++ b/LBO_Complex_Template_IRR_MoM.xlsx
@@ -94,61 +94,61 @@
     <numFmt numFmtId="187" formatCode="0\A"/>
     <numFmt numFmtId="188" formatCode="General\ &quot;yrs&quot;"/>
     <numFmt numFmtId="189" formatCode="0.000%"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0\)"/>
-    <numFmt numFmtId="191" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="192" formatCode="0.0\ \x"/>
-    <numFmt numFmtId="193" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
-    <numFmt numFmtId="194" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="195" formatCode="0.0%_);\(0.0%\)"/>
-    <numFmt numFmtId="196" formatCode="0.000\ \x&quot;rate&quot;"/>
-    <numFmt numFmtId="197" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="198" formatCode="0.00_);\(0.00\);0.00"/>
-    <numFmt numFmtId="199" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="200" formatCode="#,##0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="201" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="202" formatCode="mmm\-d\-yyyy"/>
-    <numFmt numFmtId="203" formatCode="mmm\-yyyy"/>
-    <numFmt numFmtId="204" formatCode="yyyy"/>
-    <numFmt numFmtId="205" formatCode="0.00\x&quot;rate&quot;"/>
-    <numFmt numFmtId="206" formatCode="0.0&quot;  &quot;"/>
-    <numFmt numFmtId="207" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="208" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="209" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="210" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
-    <numFmt numFmtId="211" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="212" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
-    <numFmt numFmtId="213" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="214" formatCode="#,##0.00;\(#,##0.00\)"/>
-    <numFmt numFmtId="215" formatCode=".%\,\(0.0%%;\t"/>
-    <numFmt numFmtId="216" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="217" formatCode="0.0%_);[Red]\(0.0%\)"/>
-    <numFmt numFmtId="218" formatCode="0.00_);\(0.00\);0.00_)"/>
-    <numFmt numFmtId="219" formatCode="#,##0\x"/>
-    <numFmt numFmtId="220" formatCode="&quot;TKR&quot;\ 0"/>
-    <numFmt numFmtId="221" formatCode=".%\,\(0.%%;\t"/>
-    <numFmt numFmtId="222" formatCode="&quot;$&quot;#,###.0\ \ "/>
-    <numFmt numFmtId="223" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
-    <numFmt numFmtId="224" formatCode="#,##0.000_);\(#,##0.000\)"/>
-    <numFmt numFmtId="225" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
-    <numFmt numFmtId="226" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="227" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
-    <numFmt numFmtId="228" formatCode="0.0\ "/>
-    <numFmt numFmtId="229" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="230" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
-    <numFmt numFmtId="231" formatCode="0.00\%;\-0.00\%;0.00\%"/>
-    <numFmt numFmtId="232" formatCode="0.0%\ ;\(0.0%\)"/>
-    <numFmt numFmtId="233" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="234" formatCode="&quot;$&quot;0.00\ "/>
-    <numFmt numFmtId="235" formatCode="0.0\ \ \ \ \ "/>
-    <numFmt numFmtId="236" formatCode="0.00\x;\-0.00\x;0.00\x"/>
-    <numFmt numFmtId="237" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="238" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
-    <numFmt numFmtId="239" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="240" formatCode="0.00%_);[Red]\(0.00%\)"/>
-    <numFmt numFmtId="241" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
-    <numFmt numFmtId="242" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
-    <numFmt numFmtId="243" formatCode="###0&quot;E&quot;_)"/>
-    <numFmt numFmtId="244" formatCode="#,##0.0"/>
+    <numFmt numFmtId="190" formatCode="#,##0.0"/>
+    <numFmt numFmtId="191" formatCode="#,##0.00_);\(#,##0\)"/>
+    <numFmt numFmtId="192" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="193" formatCode="0.0\ \x"/>
+    <numFmt numFmtId="194" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
+    <numFmt numFmtId="195" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="196" formatCode="0.0%_);\(0.0%\)"/>
+    <numFmt numFmtId="197" formatCode="0.000\ \x&quot;rate&quot;"/>
+    <numFmt numFmtId="198" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
+    <numFmt numFmtId="199" formatCode="0.00_);\(0.00\);0.00"/>
+    <numFmt numFmtId="200" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="201" formatCode="#,##0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="202" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="203" formatCode="mmm\-d\-yyyy"/>
+    <numFmt numFmtId="204" formatCode="mmm\-yyyy"/>
+    <numFmt numFmtId="205" formatCode="yyyy"/>
+    <numFmt numFmtId="206" formatCode="0.00\x&quot;rate&quot;"/>
+    <numFmt numFmtId="207" formatCode="0.0&quot;  &quot;"/>
+    <numFmt numFmtId="208" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="209" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="210" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="211" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
+    <numFmt numFmtId="212" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="213" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
+    <numFmt numFmtId="214" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="215" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="216" formatCode=".%\,\(0.0%%;\t"/>
+    <numFmt numFmtId="217" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="218" formatCode="0.0%_);[Red]\(0.0%\)"/>
+    <numFmt numFmtId="219" formatCode="0.00_);\(0.00\);0.00_)"/>
+    <numFmt numFmtId="220" formatCode="#,##0\x"/>
+    <numFmt numFmtId="221" formatCode="&quot;TKR&quot;\ 0"/>
+    <numFmt numFmtId="222" formatCode=".%\,\(0.%%;\t"/>
+    <numFmt numFmtId="223" formatCode="&quot;$&quot;#,###.0\ \ "/>
+    <numFmt numFmtId="224" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
+    <numFmt numFmtId="225" formatCode="#,##0.000_);\(#,##0.000\)"/>
+    <numFmt numFmtId="226" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
+    <numFmt numFmtId="227" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="228" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
+    <numFmt numFmtId="229" formatCode="0.0\ "/>
+    <numFmt numFmtId="230" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="231" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
+    <numFmt numFmtId="232" formatCode="0.00\%;\-0.00\%;0.00\%"/>
+    <numFmt numFmtId="233" formatCode="0.0%\ ;\(0.0%\)"/>
+    <numFmt numFmtId="234" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="235" formatCode="&quot;$&quot;0.00\ "/>
+    <numFmt numFmtId="236" formatCode="0.0\ \ \ \ \ "/>
+    <numFmt numFmtId="237" formatCode="0.00\x;\-0.00\x;0.00\x"/>
+    <numFmt numFmtId="238" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="239" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
+    <numFmt numFmtId="240" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="241" formatCode="0.00%_);[Red]\(0.00%\)"/>
+    <numFmt numFmtId="242" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
+    <numFmt numFmtId="243" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
+    <numFmt numFmtId="244" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
   <fonts count="105">
     <font>
@@ -1438,19 +1438,19 @@
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="191" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="191" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="192" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="191" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="193" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="194" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="192" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="194" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="196" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="196" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="197" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0"/>
@@ -1477,7 +1477,7 @@
     <xf numFmtId="0" fontId="15" fillId="20" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1486,10 +1486,10 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="5"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="6"/>
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="6"/>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="7"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1507,35 +1507,35 @@
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="198" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="199" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="7" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="5" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="199" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="200" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="200" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="201" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="200" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="202" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="201" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="15" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="202" fontId="25" fillId="24" borderId="0"/>
-    <xf numFmtId="203" fontId="27" fillId="0" borderId="8"/>
+    <xf numFmtId="203" fontId="25" fillId="24" borderId="0"/>
+    <xf numFmtId="204" fontId="27" fillId="0" borderId="8"/>
     <xf numFmtId="14" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="204" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="205" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="205" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="206" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1543,48 +1543,48 @@
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="7" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="206" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="207" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="208" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="207" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="208" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="209" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="210" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="210" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="211" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="211" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="212" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="212" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="213" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="213" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="214" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="10" fillId="0" borderId="10"/>
-    <xf numFmtId="214" fontId="10" fillId="2" borderId="9" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="196" fontId="10" fillId="0" borderId="10"/>
     <xf numFmtId="215" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="214" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="216" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="215" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="217" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0"/>
-    <xf numFmtId="217" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="218" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="196" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="13" fillId="26" borderId="11"/>
+    <xf numFmtId="217" fontId="13" fillId="26" borderId="11"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="12"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="14"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="216" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="217" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
@@ -1598,7 +1598,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="17" fontId="39" fillId="27" borderId="0"/>
-    <xf numFmtId="218" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="219" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1609,26 +1609,26 @@
     <xf numFmtId="173" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="219" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="220" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="220" fontId="10" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="221" fontId="10" fillId="25" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="221" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="222" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="219" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="220" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="42" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="196" fontId="42" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="42" fillId="0" borderId="0"/>
-    <xf numFmtId="222" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="196" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="223" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="223" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="224" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="1" hidden="1"/>
@@ -1637,62 +1637,62 @@
     <xf numFmtId="37" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="175" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="224" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="225" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="225" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="226" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="29" borderId="17"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="226" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="227" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="44" fillId="21" borderId="18"/>
-    <xf numFmtId="227" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="228" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="228" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="229" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="229" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="230" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="191" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="230" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="231" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="192" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="231" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="232" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="218" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="0" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="217" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="193" fontId="10" fillId="2" borderId="19" applyAlignment="1">
+    <xf numFmtId="194" fontId="10" fillId="2" borderId="19" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="232" fontId="46" fillId="2" borderId="0"/>
-    <xf numFmtId="233" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="233" fontId="46" fillId="2" borderId="0"/>
+    <xf numFmtId="234" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="234" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="235" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="235" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="236" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="236" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="237" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="217" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1700,10 +1700,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="198" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="237" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="238" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="38" fontId="12" fillId="0" borderId="0"/>
@@ -1721,40 +1721,40 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="238" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="239" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="239" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="240" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="209" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="240" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="210" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="241" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="240" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="240" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="241" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="241" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="240" fontId="58" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="241" fontId="58" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="217" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="217" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="59" fillId="0" borderId="0"/>
-    <xf numFmtId="241" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="242" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="243" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="61" fillId="1" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="216" fontId="62" fillId="0" borderId="0"/>
+    <xf numFmtId="217" fontId="62" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="63" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1763,10 +1763,10 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="21"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="243" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="237" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="244" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="238" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="556">
+  <cellXfs count="558">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2729,9 +2729,9 @@
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="244" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="244" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="104" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2744,6 +2744,8 @@
     <xf numFmtId="9" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="182" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4792,9 +4794,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B8:M42"/>
+  <dimension ref="B2:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo (GTM) LBO</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="26.25" customHeight="1" s="244">
       <c r="B8" s="402" t="inlineStr">
         <is>
@@ -4826,21 +4835,28 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>ADDED: ZoomInfo FY2025 S&amp;M → AI SDR margin model</t>
+          <t>MODEL1: LBO inputs overwritten with ZoomInfo FY2025 10-K / Q2 2026 BS + market price</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>See sheets ZI_Cover through ZI_05_Sensitivity (10-K sourced; IRR/MoM still on LBO sheet ~row 235)</t>
+          <t>Price $4.31, shares 292.3m, EBITDA $314.5m, debt $1269.9m, cash $150.1m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Original WSP LBO+DCF template preserved on LBO / DCF / Shares / 52wkHL tabs</t>
+          <t>Entry offer $5.39/sh (+25%); exit 8.0x; sponsor MoIC 2.97x / IRR 24.3% (illustrative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S&amp;M AI thesis: SG&amp;A margin compressed ~500bps of revenue by Y3 in forecast (see ZI_* tabs)</t>
         </is>
       </c>
     </row>
@@ -4860,8 +4876,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="55" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
@@ -4869,7 +4885,6 @@
     <col width="12" customWidth="1" style="244" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -4877,14 +4892,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="542" t="inlineStr">
         <is>
           <t>FY2025 baseline Revenue ($m)</t>
         </is>
       </c>
-      <c r="C4" s="545">
+      <c r="C4" s="557">
         <f>'ZI_01_10K_Source'!E5</f>
         <v/>
       </c>
@@ -4895,7 +4909,7 @@
           <t>FY2025 GAAP EBITDA proxy ($m)</t>
         </is>
       </c>
-      <c r="C5" s="545">
+      <c r="C5" s="557">
         <f>'ZI_01_10K_Source'!E20</f>
         <v/>
       </c>
@@ -4927,12 +4941,11 @@
           <t>Required incremental EBITDA ($m)</t>
         </is>
       </c>
-      <c r="C8" s="545">
+      <c r="C8" s="557">
         <f>C4*C7/10000</f>
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="B10" s="542" t="inlineStr">
         <is>
@@ -4955,15 +4968,15 @@
           <t>Revenue (flat case for margin math)</t>
         </is>
       </c>
-      <c r="C11" s="545">
+      <c r="C11" s="557">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="D11" s="545">
+      <c r="D11" s="557">
         <f>$C$4</f>
         <v/>
       </c>
-      <c r="E11" s="545">
+      <c r="E11" s="557">
         <f>$C$4</f>
         <v/>
       </c>
@@ -4974,15 +4987,15 @@
           <t>Net EBITDA benefit from program</t>
         </is>
       </c>
-      <c r="C12" s="545">
+      <c r="C12" s="557">
         <f>'ZI_03_Headcount_AI'!C39</f>
         <v/>
       </c>
-      <c r="D12" s="545">
+      <c r="D12" s="557">
         <f>'ZI_03_Headcount_AI'!D39</f>
         <v/>
       </c>
-      <c r="E12" s="545">
+      <c r="E12" s="557">
         <f>'ZI_03_Headcount_AI'!E39</f>
         <v/>
       </c>
@@ -4993,15 +5006,15 @@
           <t>Run-rate benefit (ex one-time)</t>
         </is>
       </c>
-      <c r="C13" s="545">
+      <c r="C13" s="557">
         <f>'ZI_03_Headcount_AI'!C40</f>
         <v/>
       </c>
-      <c r="D13" s="545">
+      <c r="D13" s="557">
         <f>'ZI_03_Headcount_AI'!D40</f>
         <v/>
       </c>
-      <c r="E13" s="545">
+      <c r="E13" s="557">
         <f>'ZI_03_Headcount_AI'!E40</f>
         <v/>
       </c>
@@ -5012,15 +5025,15 @@
           <t>Pro forma EBITDA</t>
         </is>
       </c>
-      <c r="C14" s="545">
+      <c r="C14" s="557">
         <f>$C$5+C12</f>
         <v/>
       </c>
-      <c r="D14" s="545">
+      <c r="D14" s="557">
         <f>$C$5+D12</f>
         <v/>
       </c>
-      <c r="E14" s="545">
+      <c r="E14" s="557">
         <f>$C$5+E12</f>
         <v/>
       </c>
@@ -5050,15 +5063,15 @@
           <t>Margin expansion (bps)</t>
         </is>
       </c>
-      <c r="C16" s="545">
+      <c r="C16" s="557">
         <f>(C15-$C$6)*10000</f>
         <v/>
       </c>
-      <c r="D16" s="545">
+      <c r="D16" s="557">
         <f>(D15-$C$6)*10000</f>
         <v/>
       </c>
-      <c r="E16" s="545">
+      <c r="E16" s="557">
         <f>(E15-$C$6)*10000</f>
         <v/>
       </c>
@@ -5069,15 +5082,15 @@
           <t>Run-rate expansion (bps)</t>
         </is>
       </c>
-      <c r="C17" s="545">
+      <c r="C17" s="557">
         <f>(C13/$C$4)*10000</f>
         <v/>
       </c>
-      <c r="D17" s="545">
+      <c r="D17" s="557">
         <f>(D13/$C$4)*10000</f>
         <v/>
       </c>
-      <c r="E17" s="545">
+      <c r="E17" s="557">
         <f>(E13/$C$4)*10000</f>
         <v/>
       </c>
@@ -5101,7 +5114,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="542" t="inlineStr">
         <is>
@@ -5126,15 +5138,15 @@
           <t>PF S&amp;M $ (baseline − SDR save + AI/oversight)</t>
         </is>
       </c>
-      <c r="C22" s="545">
+      <c r="C22" s="557">
         <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!C34+'ZI_03_Headcount_AI'!C35+'ZI_03_Headcount_AI'!C36</f>
         <v/>
       </c>
-      <c r="D22" s="545">
+      <c r="D22" s="557">
         <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!D34+'ZI_03_Headcount_AI'!D35+'ZI_03_Headcount_AI'!D36</f>
         <v/>
       </c>
-      <c r="E22" s="545">
+      <c r="E22" s="557">
         <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!E34+'ZI_03_Headcount_AI'!E35+'ZI_03_Headcount_AI'!E36</f>
         <v/>
       </c>
@@ -5158,7 +5170,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
@@ -5177,8 +5188,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" style="244" min="2" max="2"/>
     <col width="10" customWidth="1" style="244" min="3" max="3"/>
@@ -5189,7 +5200,6 @@
     <col width="10" customWidth="1" style="244" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -5204,7 +5214,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="542" t="inlineStr">
         <is>
@@ -5222,7 +5231,7 @@
           <t>SDR cost $k</t>
         </is>
       </c>
-      <c r="C6" s="545">
+      <c r="C6" s="557">
         <f>'ZI_03_Headcount_AI'!C8</f>
         <v/>
       </c>
@@ -5244,7 +5253,7 @@
           <t>Oversight $k</t>
         </is>
       </c>
-      <c r="C8" s="545">
+      <c r="C8" s="557">
         <f>'ZI_03_Headcount_AI'!C15</f>
         <v/>
       </c>
@@ -5255,12 +5264,11 @@
           <t>Revenue $m</t>
         </is>
       </c>
-      <c r="C9" s="545">
+      <c r="C9" s="557">
         <f>'ZI_01_10K_Source'!E5</f>
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
@@ -5460,15 +5468,13 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="B20" s="542" t="inlineStr">
         <is>
           <t>Base case Y3 run-rate bps (from bridge)</t>
         </is>
       </c>
-      <c r="C20" s="545">
+      <c r="C20" s="557">
         <f>'ZI_04_EBITDA_Bridge'!E17</f>
         <v/>
       </c>
@@ -5485,7 +5491,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:R393"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="44.140625" customWidth="1" style="244" min="2" max="2"/>
@@ -5498,7 +5504,7 @@
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Leveraged buyout model for BMC</t>
+          <t>Leveraged buyout model for ZoomInfo (GTM) — vengeanceaiUSC-LBOMODEL1</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
@@ -5548,7 +5554,7 @@
       </c>
       <c r="D6" s="378" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5566,7 @@
       </c>
       <c r="D7" s="378" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="F7" s="100" t="inlineStr">
@@ -5569,7 +5575,7 @@
         </is>
       </c>
       <c r="H7" s="406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="407" t="n">
         <v>1</v>
@@ -5585,7 +5591,7 @@
         </is>
       </c>
       <c r="D8" s="135" t="n">
-        <v>45.42</v>
+        <v>4.31</v>
       </c>
       <c r="H8" s="409" t="inlineStr">
         <is>
@@ -5610,7 +5616,7 @@
         </is>
       </c>
       <c r="D9" s="365" t="n">
-        <v>41400</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="10">
@@ -5630,13 +5636,13 @@
         </is>
       </c>
       <c r="H10" s="140" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
       <c r="I10" s="140" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
       <c r="J10" s="140" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
     </row>
     <row r="11">
@@ -5646,13 +5652,13 @@
         </is>
       </c>
       <c r="H11" s="411" t="n">
-        <v>7.325281805823042</v>
+        <v>8.57</v>
       </c>
       <c r="I11" s="412" t="n">
-        <v>7.3</v>
+        <v>8.57</v>
       </c>
       <c r="J11" s="411" t="n">
-        <v>7.325281805823042</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="12">
@@ -5669,13 +5675,13 @@
         </is>
       </c>
       <c r="H12" s="57" t="n">
-        <v>6466.026250000001</v>
+        <v>2694.6</v>
       </c>
       <c r="I12" s="57" t="n">
-        <v>6443.710000000002</v>
+        <v>2694.6</v>
       </c>
       <c r="J12" s="57" t="n">
-        <v>6466.026250000001</v>
+        <v>2694.6</v>
       </c>
     </row>
     <row r="13">
@@ -5685,7 +5691,7 @@
         </is>
       </c>
       <c r="D13" s="413" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
     </row>
     <row r="14">
@@ -5695,7 +5701,7 @@
         </is>
       </c>
       <c r="D14" s="228" t="n">
-        <v>-1306</v>
+        <v>-1269.9</v>
       </c>
       <c r="F14" s="159" t="inlineStr">
         <is>
@@ -5703,13 +5709,13 @@
         </is>
       </c>
       <c r="H14" s="140" t="n">
-        <v>-1306</v>
+        <v>-1269.9</v>
       </c>
       <c r="I14" s="140" t="n">
-        <v>-1306</v>
+        <v>-1269.9</v>
       </c>
       <c r="J14" s="140" t="n">
-        <v>-1306</v>
+        <v>-1269.9</v>
       </c>
     </row>
     <row r="15">
@@ -5719,7 +5725,7 @@
         </is>
       </c>
       <c r="D15" s="228" t="n">
-        <v>1581.9</v>
+        <v>150.1</v>
       </c>
       <c r="F15" s="159" t="inlineStr">
         <is>
@@ -5727,13 +5733,13 @@
         </is>
       </c>
       <c r="H15" s="140" t="n">
-        <v>1581.9</v>
+        <v>150.1</v>
       </c>
       <c r="I15" s="140" t="n">
-        <v>1581.9</v>
+        <v>150.1</v>
       </c>
       <c r="J15" s="140" t="n">
-        <v>1581.9</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="16">
@@ -5743,7 +5749,7 @@
         </is>
       </c>
       <c r="D16" s="228" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -5753,7 +5759,7 @@
         </is>
       </c>
       <c r="D17" s="412" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -5761,13 +5767,13 @@
         </is>
       </c>
       <c r="H17" s="57" t="n">
-        <v>6741.92625</v>
+        <v>1574.8</v>
       </c>
       <c r="I17" s="57" t="n">
-        <v>6719.610000000002</v>
+        <v>1574.8</v>
       </c>
       <c r="J17" s="57" t="n">
-        <v>6741.92625</v>
+        <v>1574.8</v>
       </c>
     </row>
     <row r="18">
@@ -5778,13 +5784,13 @@
         </is>
       </c>
       <c r="H18" s="415" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="I18" s="413" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="J18" s="413" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="K18" s="416" t="n"/>
       <c r="L18" s="416" t="n"/>
@@ -5807,7 +5813,7 @@
         </is>
       </c>
       <c r="D20" s="417" t="n">
-        <v>6741.92625</v>
+        <v>1574.8</v>
       </c>
       <c r="E20" s="418" t="n"/>
       <c r="F20" s="3" t="inlineStr">
@@ -5816,13 +5822,13 @@
         </is>
       </c>
       <c r="H20" s="307" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
       <c r="I20" s="307" t="n">
-        <v>46.09690924756112</v>
+        <v>5.3875</v>
       </c>
       <c r="J20" s="366" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
       <c r="K20" s="416" t="n"/>
       <c r="L20" s="416" t="n"/>
@@ -5834,7 +5840,7 @@
         </is>
       </c>
       <c r="D21" s="417" t="n">
-        <v>1306</v>
+        <v>1269.9</v>
       </c>
       <c r="E21" s="418" t="n"/>
       <c r="F21" s="158" t="inlineStr">
@@ -5843,13 +5849,13 @@
         </is>
       </c>
       <c r="H21" s="418" t="n">
-        <v>0.01827388815499775</v>
+        <v>0.25</v>
       </c>
       <c r="I21" s="418" t="n">
-        <v>0.01490332997712729</v>
+        <v>0.25</v>
       </c>
       <c r="J21" s="418" t="n">
-        <v>0.01827388815499775</v>
+        <v>0.25</v>
       </c>
       <c r="K21" s="416" t="n"/>
       <c r="L21" s="416" t="n"/>
@@ -5861,7 +5867,7 @@
         </is>
       </c>
       <c r="D22" s="419" t="n">
-        <v>204.52769</v>
+        <v>31.5</v>
       </c>
       <c r="H22" s="158" t="n"/>
       <c r="J22" s="420" t="n"/>
@@ -5875,7 +5881,7 @@
         </is>
       </c>
       <c r="D23" s="421" t="n">
-        <v>8252.453940000001</v>
+        <v>2876.2</v>
       </c>
       <c r="H23" s="158" t="n"/>
       <c r="J23" s="420" t="n"/>
@@ -5947,10 +5953,10 @@
         </is>
       </c>
       <c r="C27" s="422" t="n">
-        <v>1.588195309844794</v>
+        <v>0.318</v>
       </c>
       <c r="D27" s="417" t="n">
-        <v>1401.9</v>
+        <v>100.1</v>
       </c>
       <c r="F27" s="100" t="inlineStr">
         <is>
@@ -5995,10 +6001,10 @@
         </is>
       </c>
       <c r="C29" s="427" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="D29" s="417" t="n">
-        <v>2886.429000000001</v>
+        <v>786.2</v>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
@@ -6025,10 +6031,10 @@
         </is>
       </c>
       <c r="C30" s="427" t="n">
-        <v>0.76</v>
+        <v>1.5</v>
       </c>
       <c r="D30" s="417" t="n">
-        <v>670.8520000000002</v>
+        <v>471.8</v>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
@@ -6057,10 +6063,10 @@
         </is>
       </c>
       <c r="C31" s="427" t="n">
-        <v>1.85</v>
+        <v>1</v>
       </c>
       <c r="D31" s="417" t="n">
-        <v>1632.995000000001</v>
+        <v>314.5</v>
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
@@ -6132,7 +6138,7 @@
         </is>
       </c>
       <c r="H33" s="421" t="n">
-        <v>69.68916500000003</v>
+        <v>23.6</v>
       </c>
       <c r="I33" s="202" t="n"/>
       <c r="J33" s="417" t="n">
@@ -6164,10 +6170,10 @@
         </is>
       </c>
       <c r="C35" s="422" t="n">
-        <v>1.880908507986857</v>
+        <v>3.827</v>
       </c>
       <c r="D35" s="428" t="n">
-        <v>1660.277939999999</v>
+        <v>1203.6</v>
       </c>
       <c r="F35" s="34" t="n"/>
       <c r="G35" s="296" t="inlineStr">
@@ -6190,10 +6196,10 @@
         </is>
       </c>
       <c r="C36" s="430" t="n">
-        <v>9.349103817831651</v>
+        <v>9.145</v>
       </c>
       <c r="D36" s="421" t="n">
-        <v>8252.453940000001</v>
+        <v>2876.2</v>
       </c>
       <c r="F36" s="332" t="inlineStr">
         <is>
@@ -6204,10 +6210,9 @@
         <v>0.02</v>
       </c>
       <c r="H36" s="421" t="n">
-        <v>134.838525</v>
-      </c>
-    </row>
-    <row r="37"/>
+        <v>31.5</v>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -6235,28 +6240,28 @@
         </is>
       </c>
       <c r="C39" s="270" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="D39" s="270" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="E39" s="431" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="F39" s="157" t="n">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="G39" s="157" t="n">
-        <v>2015</v>
+        <v>2027</v>
       </c>
       <c r="H39" s="157" t="n">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="I39" s="157" t="n">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="J39" s="157" t="n">
-        <v>2018</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="40">
@@ -6266,28 +6271,28 @@
         </is>
       </c>
       <c r="C40" s="19" t="n">
-        <v>40633</v>
+        <v>45291</v>
       </c>
       <c r="D40" s="19" t="n">
-        <v>40999</v>
+        <v>45657</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>41364</v>
+        <v>46022</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>41729</v>
+        <v>46387</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>42094</v>
+        <v>46752</v>
       </c>
       <c r="H40" s="20" t="n">
-        <v>42460</v>
+        <v>47118</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>42825</v>
+        <v>47483</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>43190</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="41">
@@ -6308,28 +6313,28 @@
         </is>
       </c>
       <c r="C42" s="432" t="n">
-        <v>2065.3</v>
+        <v>1239.5</v>
       </c>
       <c r="D42" s="432" t="n">
-        <v>2172</v>
+        <v>1214.3</v>
       </c>
       <c r="E42" s="432" t="n">
-        <v>2201.4</v>
+        <v>1249.5</v>
       </c>
       <c r="F42" s="413" t="n">
-        <v>2278.449</v>
+        <v>1299.5</v>
       </c>
       <c r="G42" s="413" t="n">
-        <v>2403.763695</v>
+        <v>1364.5</v>
       </c>
       <c r="H42" s="413" t="n">
-        <v>2547.9895167</v>
+        <v>1432.7</v>
       </c>
       <c r="I42" s="413" t="n">
-        <v>2675.388992535</v>
+        <v>1490</v>
       </c>
       <c r="J42" s="413" t="n">
-        <v>2803.807664176681</v>
+        <v>1534.7</v>
       </c>
     </row>
     <row r="43">
@@ -6339,28 +6344,28 @@
         </is>
       </c>
       <c r="C43" s="432" t="n">
-        <v>-485.2</v>
+        <v>-200.4</v>
       </c>
       <c r="D43" s="432" t="n">
-        <v>-568.9</v>
+        <v>-211.4</v>
       </c>
       <c r="E43" s="432" t="n">
-        <v>-592</v>
+        <v>-220.5</v>
       </c>
       <c r="F43" s="413" t="n">
-        <v>-581.5921997023499</v>
+        <v>-222.8</v>
       </c>
       <c r="G43" s="413" t="n">
-        <v>-601.5609522109792</v>
+        <v>-234</v>
       </c>
       <c r="H43" s="413" t="n">
-        <v>-624.914661760138</v>
+        <v>-245.7</v>
       </c>
       <c r="I43" s="413" t="n">
-        <v>-642.7834498854697</v>
+        <v>-255.5</v>
       </c>
       <c r="J43" s="413" t="n">
-        <v>-659.618017159089</v>
+        <v>-263.2</v>
       </c>
     </row>
     <row r="44">
@@ -6370,28 +6375,28 @@
         </is>
       </c>
       <c r="C44" s="433" t="n">
-        <v>1580.1</v>
+        <v>1039.1</v>
       </c>
       <c r="D44" s="433" t="n">
-        <v>1603.1</v>
+        <v>1002.9</v>
       </c>
       <c r="E44" s="433" t="n">
-        <v>1609.4</v>
+        <v>1029</v>
       </c>
       <c r="F44" s="433" t="n">
-        <v>1696.85680029765</v>
+        <v>1076.7</v>
       </c>
       <c r="G44" s="433" t="n">
-        <v>1802.202742789021</v>
+        <v>1130.5</v>
       </c>
       <c r="H44" s="433" t="n">
-        <v>1923.074854939862</v>
+        <v>1187</v>
       </c>
       <c r="I44" s="433" t="n">
-        <v>2032.605542649531</v>
+        <v>1234.5</v>
       </c>
       <c r="J44" s="433" t="n">
-        <v>2144.189647017592</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="45">
@@ -6401,28 +6406,28 @@
         </is>
       </c>
       <c r="C45" s="432" t="n">
-        <v>-181.6</v>
+        <v>-191.5</v>
       </c>
       <c r="D45" s="432" t="n">
-        <v>-165.2</v>
+        <v>-196.1</v>
       </c>
       <c r="E45" s="432" t="n">
-        <v>-174.6</v>
+        <v>-182</v>
       </c>
       <c r="F45" s="413" t="n">
-        <v>-184.7831333486259</v>
+        <v>-189.3</v>
       </c>
       <c r="G45" s="413" t="n">
-        <v>-194.9462056828004</v>
+        <v>-198.7</v>
       </c>
       <c r="H45" s="413" t="n">
-        <v>-206.6429780237684</v>
+        <v>-208.7</v>
       </c>
       <c r="I45" s="413" t="n">
-        <v>-216.9751269249568</v>
+        <v>-217</v>
       </c>
       <c r="J45" s="413" t="n">
-        <v>-227.3899330173548</v>
+        <v>-223.5</v>
       </c>
     </row>
     <row r="46">
@@ -6432,28 +6437,28 @@
         </is>
       </c>
       <c r="C46" s="432" t="n">
-        <v>-865.6999999999999</v>
+        <v>-588.1</v>
       </c>
       <c r="D46" s="432" t="n">
-        <v>-894</v>
+        <v>-709.4</v>
       </c>
       <c r="E46" s="432" t="n">
-        <v>-969.3999999999999</v>
+        <v>-621.3</v>
       </c>
       <c r="F46" s="413" t="n">
-        <v>-965.3960306852802</v>
+        <v>-620.2</v>
       </c>
       <c r="G46" s="413" t="n">
-        <v>-994.4551754229706</v>
+        <v>-630.7</v>
       </c>
       <c r="H46" s="413" t="n">
-        <v>-1028.642590781349</v>
+        <v>-640.7</v>
       </c>
       <c r="I46" s="413" t="n">
-        <v>-1053.320830395066</v>
+        <v>-658.9</v>
       </c>
       <c r="J46" s="413" t="n">
-        <v>-1075.842153612263</v>
+        <v>-678.7</v>
       </c>
     </row>
     <row r="47">
@@ -6466,19 +6471,19 @@
       <c r="D47" s="432" t="n"/>
       <c r="E47" s="432" t="n"/>
       <c r="F47" s="413" t="n">
-        <v>-52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="G47" s="413" t="n">
-        <v>-52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="H47" s="413" t="n">
-        <v>-52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="I47" s="413" t="n">
-        <v>-52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="J47" s="413" t="n">
-        <v>-52.99732208333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6488,28 +6493,28 @@
         </is>
       </c>
       <c r="C48" s="433" t="n">
-        <v>532.8000000000003</v>
+        <v>259.5</v>
       </c>
       <c r="D48" s="433" t="n">
-        <v>543.8999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E48" s="433" t="n">
-        <v>465.4000000000003</v>
+        <v>225.7</v>
       </c>
       <c r="F48" s="433" t="n">
-        <v>493.6803141804108</v>
+        <v>267.2</v>
       </c>
       <c r="G48" s="433" t="n">
-        <v>559.8040395999167</v>
+        <v>301</v>
       </c>
       <c r="H48" s="433" t="n">
-        <v>634.7919640514119</v>
+        <v>337.6</v>
       </c>
       <c r="I48" s="433" t="n">
-        <v>709.3122632461741</v>
+        <v>358.5</v>
       </c>
       <c r="J48" s="433" t="n">
-        <v>787.9602383046408</v>
+        <v>369.3</v>
       </c>
       <c r="K48" s="140" t="n"/>
     </row>
@@ -6520,28 +6525,28 @@
         </is>
       </c>
       <c r="C49" s="432" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D49" s="432" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="E49" s="432" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="F49" s="417" t="n">
-        <v>0.9286713286713288</v>
+        <v>0</v>
       </c>
       <c r="G49" s="417" t="n">
-        <v>0.9286713286713288</v>
+        <v>0</v>
       </c>
       <c r="H49" s="417" t="n">
-        <v>0.9286713286713288</v>
+        <v>0</v>
       </c>
       <c r="I49" s="417" t="n">
-        <v>0.9286713286713288</v>
+        <v>0</v>
       </c>
       <c r="J49" s="417" t="n">
-        <v>0.9286713286713283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6551,28 +6556,28 @@
         </is>
       </c>
       <c r="C50" s="432" t="n">
-        <v>-19.8</v>
+        <v>-45.2</v>
       </c>
       <c r="D50" s="432" t="n">
-        <v>-23.3</v>
+        <v>-39.3</v>
       </c>
       <c r="E50" s="432" t="n">
-        <v>-47.8</v>
+        <v>-42.6</v>
       </c>
       <c r="F50" s="417" t="n">
-        <v>-296.9412607964802</v>
+        <v>-110.1</v>
       </c>
       <c r="G50" s="417" t="n">
-        <v>-275.9548849256559</v>
+        <v>-96.90000000000001</v>
       </c>
       <c r="H50" s="417" t="n">
-        <v>-256.9076268895943</v>
+        <v>-83.7</v>
       </c>
       <c r="I50" s="417" t="n">
-        <v>-230.9705847706274</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="J50" s="417" t="n">
-        <v>-192.5062463049772</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="51">
@@ -6582,13 +6587,13 @@
         </is>
       </c>
       <c r="C51" s="432" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="D51" s="432" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="E51" s="432" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F51" s="432" t="n">
         <v>0</v>
@@ -6613,28 +6618,28 @@
         </is>
       </c>
       <c r="C52" s="433" t="n">
-        <v>531.3000000000003</v>
+        <v>214.3</v>
       </c>
       <c r="D52" s="433" t="n">
-        <v>529.9999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="E52" s="433" t="n">
-        <v>427.9000000000003</v>
+        <v>183.1</v>
       </c>
       <c r="F52" s="433" t="n">
-        <v>197.6677247126019</v>
+        <v>157.1</v>
       </c>
       <c r="G52" s="433" t="n">
-        <v>284.7778260029322</v>
+        <v>204.2</v>
       </c>
       <c r="H52" s="433" t="n">
-        <v>378.813008490489</v>
+        <v>253.9</v>
       </c>
       <c r="I52" s="433" t="n">
-        <v>479.2703498042181</v>
+        <v>288.1</v>
       </c>
       <c r="J52" s="433" t="n">
-        <v>596.382663328335</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="53">
@@ -6644,28 +6649,28 @@
         </is>
       </c>
       <c r="C53" s="432" t="n">
-        <v>-75.09999999999999</v>
+        <v>-281.5</v>
       </c>
       <c r="D53" s="432" t="n">
-        <v>-129</v>
+        <v>-2.2</v>
       </c>
       <c r="E53" s="432" t="n">
-        <v>-96.90000000000001</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="F53" s="413" t="n">
-        <v>-44.76280094566748</v>
+        <v>-33</v>
       </c>
       <c r="G53" s="413" t="n">
-        <v>-64.48929969545246</v>
+        <v>-42.9</v>
       </c>
       <c r="H53" s="413" t="n">
-        <v>-85.78401617837896</v>
+        <v>-53.3</v>
       </c>
       <c r="I53" s="413" t="n">
-        <v>-108.5330612199783</v>
+        <v>-60.5</v>
       </c>
       <c r="J53" s="413" t="n">
-        <v>-135.0537043152971</v>
+        <v>-65.5</v>
       </c>
     </row>
     <row r="54">
@@ -6675,28 +6680,28 @@
         </is>
       </c>
       <c r="C54" s="433" t="n">
-        <v>456.2000000000003</v>
+        <v>-67.2</v>
       </c>
       <c r="D54" s="433" t="n">
-        <v>400.9999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="E54" s="433" t="n">
-        <v>331.0000000000003</v>
+        <v>113</v>
       </c>
       <c r="F54" s="433" t="n">
-        <v>152.9049237669344</v>
+        <v>124.1</v>
       </c>
       <c r="G54" s="433" t="n">
-        <v>220.2885263074797</v>
+        <v>161.3</v>
       </c>
       <c r="H54" s="433" t="n">
-        <v>293.02899231211</v>
+        <v>200.6</v>
       </c>
       <c r="I54" s="433" t="n">
-        <v>370.7372885842398</v>
+        <v>227.6</v>
       </c>
       <c r="J54" s="433" t="n">
-        <v>461.3289590130379</v>
+        <v>246.5</v>
       </c>
     </row>
     <row r="55">
@@ -6731,28 +6736,28 @@
         </is>
       </c>
       <c r="C57" s="421" t="n">
-        <v>532.8000000000003</v>
+        <v>259.5</v>
       </c>
       <c r="D57" s="421" t="n">
-        <v>543.8999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E57" s="421" t="n">
-        <v>465.4000000000003</v>
+        <v>225.7</v>
       </c>
       <c r="F57" s="421" t="n">
-        <v>493.6803141804108</v>
+        <v>267.2</v>
       </c>
       <c r="G57" s="421" t="n">
-        <v>559.8040395999167</v>
+        <v>301</v>
       </c>
       <c r="H57" s="421" t="n">
-        <v>634.7919640514119</v>
+        <v>337.6</v>
       </c>
       <c r="I57" s="421" t="n">
-        <v>709.3122632461741</v>
+        <v>358.5</v>
       </c>
       <c r="J57" s="421" t="n">
-        <v>787.9602383046408</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="58">
@@ -6762,28 +6767,28 @@
         </is>
       </c>
       <c r="C58" s="432" t="n">
-        <v>190</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D58" s="432" t="n">
-        <v>224.6</v>
+        <v>85.7</v>
       </c>
       <c r="E58" s="432" t="n">
-        <v>229</v>
+        <v>88.8</v>
       </c>
       <c r="F58" s="417" t="n">
-        <v>223.946868228773</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G58" s="417" t="n">
-        <v>220.6010317460318</v>
+        <v>97</v>
       </c>
       <c r="H58" s="417" t="n">
-        <v>222.400781053162</v>
+        <v>101.8</v>
       </c>
       <c r="I58" s="417" t="n">
-        <v>224.1937314184933</v>
+        <v>105.9</v>
       </c>
       <c r="J58" s="417" t="n">
-        <v>223</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="59">
@@ -6796,19 +6801,19 @@
       <c r="D59" s="432" t="n"/>
       <c r="E59" s="432" t="n"/>
       <c r="F59" s="413" t="n">
-        <v>52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="G59" s="413" t="n">
-        <v>52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="H59" s="413" t="n">
-        <v>52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="I59" s="413" t="n">
-        <v>52.99732208333334</v>
+        <v>0</v>
       </c>
       <c r="J59" s="413" t="n">
-        <v>52.99732208333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6818,28 +6823,28 @@
         </is>
       </c>
       <c r="C60" s="432" t="n">
-        <v>106.5</v>
+        <v>167.6</v>
       </c>
       <c r="D60" s="432" t="n">
-        <v>127.2</v>
+        <v>138</v>
       </c>
       <c r="E60" s="432" t="n">
-        <v>147.4</v>
+        <v>116.2</v>
       </c>
       <c r="F60" s="417" t="n">
-        <v>161.0547368274718</v>
+        <v>120.8</v>
       </c>
       <c r="G60" s="417" t="n">
-        <v>162.0820911651659</v>
+        <v>126.9</v>
       </c>
       <c r="H60" s="417" t="n">
-        <v>163.6976202897424</v>
+        <v>133.2</v>
       </c>
       <c r="I60" s="417" t="n">
-        <v>163.5682893160696</v>
+        <v>138.6</v>
       </c>
       <c r="J60" s="417" t="n">
-        <v>162.9165586144626</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="61">
@@ -6849,22 +6854,22 @@
         </is>
       </c>
       <c r="C61" s="432" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="D61" s="432" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="E61" s="432" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="F61" s="432" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G61" s="432" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H61" s="432" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I61" s="432" t="n">
         <v>0</v>
@@ -6880,28 +6885,28 @@
         </is>
       </c>
       <c r="C62" s="433" t="n">
-        <v>843.6000000000003</v>
+        <v>340.1</v>
       </c>
       <c r="D62" s="433" t="n">
-        <v>906.4999999999999</v>
+        <v>183.1</v>
       </c>
       <c r="E62" s="433" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
       <c r="F62" s="433" t="n">
-        <v>947.6792413199889</v>
+        <v>359.6</v>
       </c>
       <c r="G62" s="433" t="n">
-        <v>1000.484484594448</v>
+        <v>398</v>
       </c>
       <c r="H62" s="433" t="n">
-        <v>1078.88768747765</v>
+        <v>439.4</v>
       </c>
       <c r="I62" s="433" t="n">
-        <v>1150.07160606407</v>
+        <v>464.4</v>
       </c>
       <c r="J62" s="433" t="n">
-        <v>1226.874119002437</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="63">
@@ -6928,25 +6933,25 @@
       </c>
       <c r="C65" s="418" t="n"/>
       <c r="D65" s="418" t="n">
-        <v>0.05166319663002938</v>
+        <v>-0.0203</v>
       </c>
       <c r="E65" s="418" t="n">
-        <v>0.01353591160221002</v>
+        <v>0.029</v>
       </c>
       <c r="F65" s="424" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="G65" s="424" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="H65" s="424" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I65" s="424" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J65" s="424" t="n">
-        <v>0.048</v>
+        <v>0.03</v>
       </c>
       <c r="K65" s="424" t="n"/>
     </row>
@@ -6957,28 +6962,28 @@
         </is>
       </c>
       <c r="C66" s="418" t="n">
-        <v>0.7650704498135864</v>
+        <v>0.8383</v>
       </c>
       <c r="D66" s="418" t="n">
-        <v>0.7380755064456721</v>
+        <v>0.8259</v>
       </c>
       <c r="E66" s="418" t="n">
-        <v>0.7310802216771146</v>
+        <v>0.8235</v>
       </c>
       <c r="F66" s="434" t="n">
-        <v>0.7447420593121242</v>
+        <v>0.8285</v>
       </c>
       <c r="G66" s="434" t="n">
-        <v>0.7497420593121242</v>
+        <v>0.8285</v>
       </c>
       <c r="H66" s="434" t="n">
-        <v>0.7547420593121242</v>
+        <v>0.8285</v>
       </c>
       <c r="I66" s="434" t="n">
-        <v>0.7597420593121242</v>
+        <v>0.8285</v>
       </c>
       <c r="J66" s="434" t="n">
-        <v>0.7647420593121242</v>
+        <v>0.8285</v>
       </c>
       <c r="K66" s="424" t="n">
         <v>0.005</v>
@@ -6991,28 +6996,28 @@
         </is>
       </c>
       <c r="C67" s="418" t="n">
-        <v>0.08792911441437078</v>
+        <v>0.1545</v>
       </c>
       <c r="D67" s="418" t="n">
-        <v>0.07605893186003683</v>
+        <v>0.1615</v>
       </c>
       <c r="E67" s="418" t="n">
-        <v>0.07931316434995911</v>
+        <v>0.1457</v>
       </c>
       <c r="F67" s="434" t="n">
-        <v>0.08110040354145558</v>
+        <v>0.1457</v>
       </c>
       <c r="G67" s="434" t="n">
-        <v>0.08110040354145558</v>
+        <v>0.1457</v>
       </c>
       <c r="H67" s="434" t="n">
-        <v>0.08110040354145558</v>
+        <v>0.1457</v>
       </c>
       <c r="I67" s="434" t="n">
-        <v>0.08110040354145558</v>
+        <v>0.1457</v>
       </c>
       <c r="J67" s="434" t="n">
-        <v>0.08110040354145558</v>
+        <v>0.1457</v>
       </c>
       <c r="K67" s="424" t="n">
         <v>0</v>
@@ -7025,28 +7030,28 @@
         </is>
       </c>
       <c r="C68" s="418" t="n">
-        <v>0.4191642860601364</v>
+        <v>0.4745</v>
       </c>
       <c r="D68" s="418" t="n">
-        <v>0.4116022099447514</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="E68" s="418" t="n">
-        <v>0.4403561370037248</v>
+        <v>0.4972</v>
       </c>
       <c r="F68" s="434" t="n">
-        <v>0.4237075443362042</v>
+        <v>0.4772</v>
       </c>
       <c r="G68" s="434" t="n">
-        <v>0.4137075443362042</v>
+        <v>0.4622</v>
       </c>
       <c r="H68" s="434" t="n">
-        <v>0.4037075443362042</v>
+        <v>0.4472</v>
       </c>
       <c r="I68" s="434" t="n">
-        <v>0.3937075443362042</v>
+        <v>0.4422</v>
       </c>
       <c r="J68" s="434" t="n">
-        <v>0.3837075443362042</v>
+        <v>0.4422</v>
       </c>
       <c r="K68" s="424" t="n">
         <v>-0.01</v>
@@ -7059,28 +7064,28 @@
         </is>
       </c>
       <c r="C69" s="418" t="n">
-        <v>0.1413514022209673</v>
+        <v>0.21</v>
       </c>
       <c r="D69" s="418" t="n">
-        <v>0.2433962264150944</v>
+        <v>0.21</v>
       </c>
       <c r="E69" s="418" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="F69" s="424" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="G69" s="434" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="H69" s="434" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="I69" s="434" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="J69" s="434" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="K69" s="424" t="n">
         <v>0</v>
@@ -7093,28 +7098,28 @@
         </is>
       </c>
       <c r="C70" s="418" t="n">
-        <v>0.06949429037520391</v>
+        <v>0.215</v>
       </c>
       <c r="D70" s="418" t="n">
-        <v>0.078127879122904</v>
+        <v>0.1524</v>
       </c>
       <c r="E70" s="418" t="n">
-        <v>0.08490783410138249</v>
+        <v>0.1447</v>
       </c>
       <c r="F70" s="424" t="n">
         <v>0.093</v>
       </c>
       <c r="G70" s="434" t="n">
-        <v>0.0905</v>
+        <v>0.093</v>
       </c>
       <c r="H70" s="434" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="I70" s="434" t="n">
-        <v>0.08549999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="J70" s="434" t="n">
-        <v>0.08299999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="K70" s="424" t="n">
         <v>-0.0025</v>
@@ -8378,7 +8383,6 @@
         <v>987.5822307314286</v>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
@@ -8445,7 +8449,6 @@
         <v>-223</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
@@ -8987,7 +8990,6 @@
         <v>586.7181807314284</v>
       </c>
     </row>
-    <row r="154"/>
     <row r="155">
       <c r="B155" s="34" t="inlineStr">
         <is>
@@ -9126,7 +9128,6 @@
         </is>
       </c>
     </row>
-    <row r="160"/>
     <row r="161">
       <c r="B161" s="321" t="inlineStr">
         <is>
@@ -10518,7 +10519,7 @@
         </is>
       </c>
       <c r="C230" s="462" t="n">
-        <v>1660.277939999999</v>
+        <v>1203.6</v>
       </c>
       <c r="D230" s="463" t="n">
         <v>1</v>
@@ -10527,19 +10528,19 @@
         <v>1</v>
       </c>
       <c r="F230" s="417" t="n">
-        <v>5695.634218624235</v>
+        <v>3041.8</v>
       </c>
       <c r="G230" s="417" t="n">
-        <v>6309.071278125453</v>
+        <v>3220.7</v>
       </c>
       <c r="H230" s="417" t="n">
-        <v>6922.508337626672</v>
+        <v>3399.6</v>
       </c>
       <c r="I230" s="417" t="n">
-        <v>7535.945397127889</v>
+        <v>3507</v>
       </c>
       <c r="J230" s="417" t="n">
-        <v>8149.38245662911</v>
+        <v>3578.6</v>
       </c>
     </row>
     <row r="231">
@@ -11336,16 +11337,16 @@
     </row>
     <row r="260">
       <c r="B260" s="469" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C260" s="468" t="n">
-        <v>3.430530564433228</v>
+        <v>2.377</v>
       </c>
       <c r="D260" s="166" t="n">
-        <v>0.2795941873668486</v>
+        <v>0.1891</v>
       </c>
       <c r="E260" s="417" t="n">
-        <v>-1660.277939999999</v>
+        <v>-1203.6</v>
       </c>
       <c r="F260" s="432" t="n">
         <v>0</v>
@@ -11360,21 +11361,21 @@
         <v>0</v>
       </c>
       <c r="J260" s="415" t="n">
-        <v>5695.634218624235</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="469" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="C261" s="468" t="n">
-        <v>3.800009098552172</v>
+        <v>2.576</v>
       </c>
       <c r="D261" s="166" t="n">
-        <v>0.3060413503798853</v>
+        <v>0.2083</v>
       </c>
       <c r="E261" s="417" t="n">
-        <v>-1660.277939999999</v>
+        <v>-1203.6</v>
       </c>
       <c r="F261" s="417" t="n">
         <v>0</v>
@@ -11389,21 +11390,21 @@
         <v>0</v>
       </c>
       <c r="J261" s="415" t="n">
-        <v>6309.071278125453</v>
+        <v>3100.2</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="469" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="C262" s="468" t="n">
-        <v>4.169487632671115</v>
+        <v>2.973</v>
       </c>
       <c r="D262" s="166" t="n">
-        <v>0.3305050828444873</v>
+        <v>0.2435</v>
       </c>
       <c r="E262" s="417" t="n">
-        <v>-1660.277939999999</v>
+        <v>-1203.6</v>
       </c>
       <c r="F262" s="417" t="n">
         <v>0</v>
@@ -11418,21 +11419,21 @@
         <v>0</v>
       </c>
       <c r="J262" s="415" t="n">
-        <v>6922.508337626672</v>
+        <v>3578.6</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="469" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="C263" s="468" t="n">
-        <v>4.538966166790057</v>
+        <v>3.371</v>
       </c>
       <c r="D263" s="166" t="n">
-        <v>0.3532916093100265</v>
+        <v>0.2751</v>
       </c>
       <c r="E263" s="417" t="n">
-        <v>-1660.277939999999</v>
+        <v>-1203.6</v>
       </c>
       <c r="F263" s="417" t="n">
         <v>0</v>
@@ -11447,21 +11448,21 @@
         <v>0</v>
       </c>
       <c r="J263" s="415" t="n">
-        <v>7535.945397127889</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="469" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="C264" s="468" t="n">
-        <v>4.908444700909001</v>
+        <v>3.569</v>
       </c>
       <c r="D264" s="166" t="n">
-        <v>0.3746393777884374</v>
+        <v>0.2898</v>
       </c>
       <c r="E264" s="417" t="n">
-        <v>-1660.277939999999</v>
+        <v>-1203.6</v>
       </c>
       <c r="F264" s="417" t="n">
         <v>0</v>
@@ -11476,13 +11477,13 @@
         <v>0</v>
       </c>
       <c r="J264" s="415" t="n">
-        <v>8149.38245662911</v>
+        <v>4296.2</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="317" t="inlineStr">
         <is>
-          <t>SUMMARY AT 7.3x EXIT EBITDA MULTIPLE</t>
+          <t>SUMMARY AT 8.0x EXIT EBITDA MULTIPLE — ZoomInfo LBOMODEL1</t>
         </is>
       </c>
       <c r="C266" s="15" t="n"/>
@@ -11679,19 +11680,19 @@
         </is>
       </c>
       <c r="F275" s="471" t="n">
-        <v>1660.277939999999</v>
+        <v>1203.6</v>
       </c>
       <c r="G275" s="472" t="n">
-        <v>0.2423567429059611</v>
+        <v>0.4185</v>
       </c>
       <c r="H275" s="472" t="n">
         <v>1</v>
       </c>
       <c r="I275" s="468" t="n">
-        <v>4.169487632671115</v>
+        <v>2.973</v>
       </c>
       <c r="J275" s="473" t="n">
-        <v>0.3305050828444873</v>
+        <v>0.2435</v>
       </c>
     </row>
     <row r="276">
@@ -12487,7 +12488,6 @@
         <v>0.2849090713511313</v>
       </c>
     </row>
-    <row r="318"/>
     <row r="319">
       <c r="B319" s="317" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:K118"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="40.28515625" customWidth="1" style="244" min="2" max="2"/>
@@ -14976,7 +14976,6 @@
         <v>0.7748616857223557</v>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
@@ -15389,7 +15388,6 @@
         <v>36.4886239211832</v>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="17.25" customHeight="1" s="244">
       <c r="C83" s="112" t="inlineStr">
         <is>
@@ -15565,7 +15563,6 @@
       <c r="D93" s="93" t="n"/>
       <c r="E93" s="93" t="n"/>
     </row>
-    <row r="94"/>
     <row r="114">
       <c r="B114" s="108" t="n"/>
       <c r="C114" s="109" t="inlineStr">
@@ -15683,7 +15680,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
@@ -15988,7 +15985,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:F268"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19.42578125" bestFit="1" customWidth="1" style="244" min="1" max="1"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="244" min="2" max="5"/>
@@ -21291,14 +21288,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="244" min="2" max="2"/>
     <col width="100" customWidth="1" style="244" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -21313,7 +21309,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
@@ -21386,7 +21381,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
@@ -21429,7 +21423,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
@@ -21439,6 +21432,13 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>SDR % of S&amp;M and AI unit costs are yellow assumptions. Illustrative — not investment advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LBOMODEL1: core LBO sheet inputs now use these ZoomInfo figures (see LBO tab).</t>
         </is>
       </c>
     </row>
@@ -21457,8 +21457,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="42" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
@@ -21467,7 +21467,6 @@
     <col width="70" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -21475,7 +21474,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="541" t="inlineStr">
         <is>
@@ -21509,13 +21507,13 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="543" t="n">
+      <c r="C5" s="556" t="n">
         <v>1239.5</v>
       </c>
-      <c r="D5" s="543" t="n">
+      <c r="D5" s="556" t="n">
         <v>1214.3</v>
       </c>
-      <c r="E5" s="543" t="n">
+      <c r="E5" s="556" t="n">
         <v>1249.5</v>
       </c>
       <c r="F5" s="542" t="inlineStr">
@@ -21530,13 +21528,13 @@
           <t>Selling &amp; Marketing</t>
         </is>
       </c>
-      <c r="C6" s="543" t="n">
+      <c r="C6" s="556" t="n">
         <v>408.5</v>
       </c>
-      <c r="D6" s="543" t="n">
+      <c r="D6" s="556" t="n">
         <v>414.1</v>
       </c>
-      <c r="E6" s="543" t="n">
+      <c r="E6" s="556" t="n">
         <v>414.6</v>
       </c>
       <c r="F6" s="542" t="inlineStr">
@@ -21551,13 +21549,13 @@
           <t>Research &amp; Development</t>
         </is>
       </c>
-      <c r="C7" s="543" t="n">
+      <c r="C7" s="556" t="n">
         <v>191.5</v>
       </c>
-      <c r="D7" s="543" t="n">
+      <c r="D7" s="556" t="n">
         <v>196.1</v>
       </c>
-      <c r="E7" s="543" t="n">
+      <c r="E7" s="556" t="n">
         <v>182</v>
       </c>
       <c r="F7" s="542" t="inlineStr">
@@ -21572,13 +21570,13 @@
           <t>General &amp; Administrative</t>
         </is>
       </c>
-      <c r="C8" s="543" t="n">
+      <c r="C8" s="556" t="n">
         <v>179.6</v>
       </c>
-      <c r="D8" s="543" t="n">
+      <c r="D8" s="556" t="n">
         <v>295.3</v>
       </c>
-      <c r="E8" s="543" t="n">
+      <c r="E8" s="556" t="n">
         <v>206.7</v>
       </c>
       <c r="F8" s="542" t="inlineStr">
@@ -21593,7 +21591,7 @@
           <t>Operating expenses (ex-COGS)</t>
         </is>
       </c>
-      <c r="E9" s="543" t="n">
+      <c r="E9" s="556" t="n">
         <v>824.2</v>
       </c>
       <c r="F9" s="542" t="inlineStr">
@@ -21608,13 +21606,13 @@
           <t>Operating income</t>
         </is>
       </c>
-      <c r="C10" s="543" t="n">
+      <c r="C10" s="556" t="n">
         <v>259.5</v>
       </c>
-      <c r="D10" s="543" t="n">
+      <c r="D10" s="556" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="E10" s="543" t="n">
+      <c r="E10" s="556" t="n">
         <v>225.7</v>
       </c>
       <c r="F10" s="542" t="inlineStr">
@@ -21629,13 +21627,13 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="543" t="n">
+      <c r="C11" s="556" t="n">
         <v>19.6</v>
       </c>
-      <c r="D11" s="543" t="n">
+      <c r="D11" s="556" t="n">
         <v>25.9</v>
       </c>
-      <c r="E11" s="543" t="n">
+      <c r="E11" s="556" t="n">
         <v>30.3</v>
       </c>
       <c r="F11" s="542" t="inlineStr">
@@ -21650,13 +21648,13 @@
           <t>Amort. of intangibles</t>
         </is>
       </c>
-      <c r="C12" s="543" t="n">
+      <c r="C12" s="556" t="n">
         <v>61</v>
       </c>
-      <c r="D12" s="543" t="n">
+      <c r="D12" s="556" t="n">
         <v>59.8</v>
       </c>
-      <c r="E12" s="543" t="n">
+      <c r="E12" s="556" t="n">
         <v>58.5</v>
       </c>
       <c r="F12" s="542" t="inlineStr">
@@ -21671,13 +21669,13 @@
           <t>Total D&amp;A (dep+intang)</t>
         </is>
       </c>
-      <c r="C13" s="543" t="n">
+      <c r="C13" s="556" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="D13" s="543" t="n">
+      <c r="D13" s="556" t="n">
         <v>85.7</v>
       </c>
-      <c r="E13" s="543" t="n">
+      <c r="E13" s="556" t="n">
         <v>88.8</v>
       </c>
       <c r="F13" s="542" t="inlineStr">
@@ -21692,13 +21690,13 @@
           <t>Share-based compensation</t>
         </is>
       </c>
-      <c r="C14" s="543" t="n">
+      <c r="C14" s="556" t="n">
         <v>167.6</v>
       </c>
-      <c r="D14" s="543" t="n">
+      <c r="D14" s="556" t="n">
         <v>138</v>
       </c>
-      <c r="E14" s="543" t="n">
+      <c r="E14" s="556" t="n">
         <v>116.2</v>
       </c>
       <c r="F14" s="542" t="inlineStr">
@@ -21713,7 +21711,7 @@
           <t>Advertising expense</t>
         </is>
       </c>
-      <c r="E15" s="543" t="n">
+      <c r="E15" s="556" t="n">
         <v>37.3</v>
       </c>
       <c r="F15" s="542" t="inlineStr">
@@ -21728,13 +21726,13 @@
           <t>Amort. deferred commissions</t>
         </is>
       </c>
-      <c r="C16" s="543" t="n">
+      <c r="C16" s="556" t="n">
         <v>75.3</v>
       </c>
-      <c r="D16" s="543" t="n">
+      <c r="D16" s="556" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="E16" s="543" t="n">
+      <c r="E16" s="556" t="n">
         <v>90.2</v>
       </c>
       <c r="F16" s="542" t="inlineStr">
@@ -21749,13 +21747,13 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C17" s="543" t="n">
+      <c r="C17" s="556" t="n">
         <v>107.3</v>
       </c>
-      <c r="D17" s="543" t="n">
+      <c r="D17" s="556" t="n">
         <v>29.1</v>
       </c>
-      <c r="E17" s="543" t="n">
+      <c r="E17" s="556" t="n">
         <v>124.2</v>
       </c>
       <c r="F17" s="542" t="inlineStr">
@@ -21764,14 +21762,13 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="544" t="inlineStr">
         <is>
           <t>Implied COGS (Rev − OpEx − OpInc)</t>
         </is>
       </c>
-      <c r="E19" s="545">
+      <c r="E19" s="557">
         <f>E5-E9-E10</f>
         <v/>
       </c>
@@ -21782,7 +21779,7 @@
           <t>GAAP EBITDA proxy (OpInc + D&amp;A)</t>
         </is>
       </c>
-      <c r="E20" s="545">
+      <c r="E20" s="557">
         <f>E10+E13</f>
         <v/>
       </c>
@@ -21804,7 +21801,7 @@
           <t>Adj. EBITDA proxy (+SBC)</t>
         </is>
       </c>
-      <c r="E22" s="545">
+      <c r="E22" s="557">
         <f>E20+E14</f>
         <v/>
       </c>
@@ -21820,7 +21817,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="547" t="inlineStr">
         <is>
@@ -21895,7 +21891,7 @@
           <t>S&amp;M $ / S&amp;M employee ($000s)</t>
         </is>
       </c>
-      <c r="E32" s="545">
+      <c r="E32" s="557">
         <f>E6*1000/E28</f>
         <v/>
       </c>
@@ -21911,7 +21907,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="B35" s="542" t="inlineStr">
         <is>
@@ -21942,14 +21937,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" style="244" min="2" max="2"/>
     <col width="14" customWidth="1" style="244" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -21957,14 +21951,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="542" t="inlineStr">
         <is>
           <t>FY2025 Revenue ($m)</t>
         </is>
       </c>
-      <c r="C4" s="545">
+      <c r="C4" s="557">
         <f>'ZI_01_10K_Source'!E5</f>
         <v/>
       </c>
@@ -21975,7 +21968,7 @@
           <t>FY2025 S&amp;M ($m)</t>
         </is>
       </c>
-      <c r="C5" s="545">
+      <c r="C5" s="557">
         <f>'ZI_01_10K_Source'!E6</f>
         <v/>
       </c>
@@ -21991,7 +21984,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="B8" s="547" t="inlineStr">
         <is>
@@ -22005,7 +21997,7 @@
           <t>Advertising</t>
         </is>
       </c>
-      <c r="C9" s="545">
+      <c r="C9" s="557">
         <f>'ZI_01_10K_Source'!E15</f>
         <v/>
       </c>
@@ -22016,7 +22008,7 @@
           <t>Deferred commission amortization</t>
         </is>
       </c>
-      <c r="C10" s="545">
+      <c r="C10" s="557">
         <f>'ZI_01_10K_Source'!E16</f>
         <v/>
       </c>
@@ -22027,7 +22019,7 @@
           <t>Residual S&amp;M (people + other)</t>
         </is>
       </c>
-      <c r="C11" s="545">
+      <c r="C11" s="557">
         <f>C5-C9-C10</f>
         <v/>
       </c>
@@ -22049,12 +22041,11 @@
           <t>Residual $ / S&amp;M employee ($000s)</t>
         </is>
       </c>
-      <c r="C13" s="545">
+      <c r="C13" s="557">
         <f>C11*1000/'ZI_01_10K_Source'!E28</f>
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="547" t="inlineStr">
         <is>
@@ -22078,7 +22069,7 @@
           <t>S&amp;M bloat vs target ($m)</t>
         </is>
       </c>
-      <c r="C17" s="545">
+      <c r="C17" s="557">
         <f>MAX(0,C5-C4*C16)</f>
         <v/>
       </c>
@@ -22105,7 +22096,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
@@ -22124,8 +22114,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
@@ -22133,7 +22123,6 @@
     <col width="12" customWidth="1" style="244" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
@@ -22141,7 +22130,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="547" t="inlineStr">
         <is>
@@ -22187,7 +22175,7 @@
           <t>Fully loaded cost / SDR / yr ($000s)</t>
         </is>
       </c>
-      <c r="C8" s="543" t="n">
+      <c r="C8" s="556" t="n">
         <v>155</v>
       </c>
     </row>
@@ -22197,12 +22185,11 @@
           <t>Addressable SDR cost pool ($m)</t>
         </is>
       </c>
-      <c r="C9" s="545">
+      <c r="C9" s="557">
         <f>C7*C8/1000</f>
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="547" t="inlineStr">
         <is>
@@ -22226,7 +22213,7 @@
           <t>AI platform + compute / seat / yr ($000s)</t>
         </is>
       </c>
-      <c r="C13" s="543" t="n">
+      <c r="C13" s="556" t="n">
         <v>15</v>
       </c>
     </row>
@@ -22246,7 +22233,7 @@
           <t>Oversight fully loaded / FTE / yr ($000s)</t>
         </is>
       </c>
-      <c r="C15" s="543" t="n">
+      <c r="C15" s="556" t="n">
         <v>150</v>
       </c>
     </row>
@@ -22256,7 +22243,7 @@
           <t>One-time severance / SDR ($000s)</t>
         </is>
       </c>
-      <c r="C16" s="543" t="n">
+      <c r="C16" s="556" t="n">
         <v>25</v>
       </c>
     </row>
@@ -22266,11 +22253,10 @@
           <t>One-time AI build / integration ($m) in Y1</t>
         </is>
       </c>
-      <c r="C17" s="543" t="n">
+      <c r="C17" s="556" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="547" t="inlineStr">
         <is>
@@ -22373,20 +22359,19 @@
           <t>Avg SDRs during year</t>
         </is>
       </c>
-      <c r="C25" s="545">
+      <c r="C25" s="557">
         <f>($C$7+C22)/2</f>
         <v/>
       </c>
-      <c r="D25" s="545">
+      <c r="D25" s="557">
         <f>(C22+D22)/2</f>
         <v/>
       </c>
-      <c r="E25" s="545">
+      <c r="E25" s="557">
         <f>(D22+E22)/2</f>
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="547" t="inlineStr">
         <is>
@@ -22400,15 +22385,15 @@
           <t>AI seats (cum.)</t>
         </is>
       </c>
-      <c r="C28" s="545">
+      <c r="C28" s="557">
         <f>C23*$C$12</f>
         <v/>
       </c>
-      <c r="D28" s="545">
+      <c r="D28" s="557">
         <f>D23*$C$12</f>
         <v/>
       </c>
-      <c r="E28" s="545">
+      <c r="E28" s="557">
         <f>E23*$C$12</f>
         <v/>
       </c>
@@ -22432,7 +22417,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="B31" s="547" t="inlineStr">
         <is>
@@ -22446,15 +22430,15 @@
           <t>SDR cash cost (avg HC × cost)</t>
         </is>
       </c>
-      <c r="C32" s="545">
+      <c r="C32" s="557">
         <f>C25*$C$8/1000</f>
         <v/>
       </c>
-      <c r="D32" s="545">
+      <c r="D32" s="557">
         <f>D25*$C$8/1000</f>
         <v/>
       </c>
-      <c r="E32" s="545">
+      <c r="E32" s="557">
         <f>E25*$C$8/1000</f>
         <v/>
       </c>
@@ -22465,15 +22449,15 @@
           <t>Baseline SDR cost if no program</t>
         </is>
       </c>
-      <c r="C33" s="545">
+      <c r="C33" s="557">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="D33" s="545">
+      <c r="D33" s="557">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="E33" s="545">
+      <c r="E33" s="557">
         <f>$C$9</f>
         <v/>
       </c>
@@ -22484,15 +22468,15 @@
           <t>Gross SDR savings vs baseline</t>
         </is>
       </c>
-      <c r="C34" s="545">
+      <c r="C34" s="557">
         <f>C33-C32</f>
         <v/>
       </c>
-      <c r="D34" s="545">
+      <c r="D34" s="557">
         <f>D33-D32</f>
         <v/>
       </c>
-      <c r="E34" s="545">
+      <c r="E34" s="557">
         <f>E33-E32</f>
         <v/>
       </c>
@@ -22503,15 +22487,15 @@
           <t>AI seat opex</t>
         </is>
       </c>
-      <c r="C35" s="545">
+      <c r="C35" s="557">
         <f>C28*$C$13/1000</f>
         <v/>
       </c>
-      <c r="D35" s="545">
+      <c r="D35" s="557">
         <f>D28*$C$13/1000</f>
         <v/>
       </c>
-      <c r="E35" s="545">
+      <c r="E35" s="557">
         <f>E28*$C$13/1000</f>
         <v/>
       </c>
@@ -22522,15 +22506,15 @@
           <t>Oversight opex</t>
         </is>
       </c>
-      <c r="C36" s="545">
+      <c r="C36" s="557">
         <f>C29*$C$15/1000</f>
         <v/>
       </c>
-      <c r="D36" s="545">
+      <c r="D36" s="557">
         <f>D29*$C$15/1000</f>
         <v/>
       </c>
-      <c r="E36" s="545">
+      <c r="E36" s="557">
         <f>E29*$C$15/1000</f>
         <v/>
       </c>
@@ -22541,15 +22525,15 @@
           <t>Severance (this year's exits)</t>
         </is>
       </c>
-      <c r="C37" s="545">
+      <c r="C37" s="557">
         <f>C24*$C$16/1000</f>
         <v/>
       </c>
-      <c r="D37" s="545">
+      <c r="D37" s="557">
         <f>D24*$C$16/1000</f>
         <v/>
       </c>
-      <c r="E37" s="545">
+      <c r="E37" s="557">
         <f>E24*$C$16/1000</f>
         <v/>
       </c>
@@ -22560,14 +22544,14 @@
           <t>AI build (Y1 only)</t>
         </is>
       </c>
-      <c r="C38" s="545">
+      <c r="C38" s="557">
         <f>$C$17</f>
         <v/>
       </c>
-      <c r="D38" s="543" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="543" t="n">
+      <c r="D38" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="556" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22577,15 +22561,15 @@
           <t>Net EBITDA benefit (in-year, after one-time)</t>
         </is>
       </c>
-      <c r="C39" s="545">
+      <c r="C39" s="557">
         <f>C34-C35-C36-C37-C38</f>
         <v/>
       </c>
-      <c r="D39" s="545">
+      <c r="D39" s="557">
         <f>D34-D35-D36-D37-D38</f>
         <v/>
       </c>
-      <c r="E39" s="545">
+      <c r="E39" s="557">
         <f>E34-E35-E36-E37-E38</f>
         <v/>
       </c>
@@ -22596,15 +22580,15 @@
           <t>Year-end run-rate benefit (ex one-time)</t>
         </is>
       </c>
-      <c r="C40" s="545">
+      <c r="C40" s="557">
         <f>(C23*$C$8/1000)-(C28*$C$13/1000)-(C29*$C$15/1000)</f>
         <v/>
       </c>
-      <c r="D40" s="545">
+      <c r="D40" s="557">
         <f>(D23*$C$8/1000)-(D28*$C$13/1000)-(D29*$C$15/1000)</f>
         <v/>
       </c>
-      <c r="E40" s="545">
+      <c r="E40" s="557">
         <f>(E23*$C$8/1000)-(E28*$C$13/1000)-(E29*$C$15/1000)</f>
         <v/>
       </c>

--- a/LBO_Complex_Template_IRR_MoM.xlsx
+++ b/LBO_Complex_Template_IRR_MoM.xlsx
@@ -4794,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M43"/>
+  <dimension ref="B2:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -4857,6 +4857,20 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>S&amp;M AI thesis: SG&amp;A margin compressed ~500bps of revenue by Y3 in forecast (see ZI_* tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Assumptions list (all tabs): LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.md|.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14082,7 @@
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Discounted Cash Flow Model for BMC</t>
+          <t>Discounted Cash Flow Model for ZoomInfo (GTM) — LBOMODEL1</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
@@ -14105,7 +14119,7 @@
         </is>
       </c>
       <c r="C6" s="511" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="7">
@@ -14115,7 +14129,7 @@
         </is>
       </c>
       <c r="C7" s="84" t="n">
-        <v>41400</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="8">
@@ -14125,7 +14139,7 @@
         </is>
       </c>
       <c r="C8" s="512" t="n">
-        <v>143.973</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="9">
@@ -14135,7 +14149,7 @@
         </is>
       </c>
       <c r="C9" s="513" t="n">
-        <v>0.06990222994664612</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="244" thickBot="1">
@@ -14160,28 +14174,28 @@
         </is>
       </c>
       <c r="C12" s="270" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="270" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="E12" s="270" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="157" t="n">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="G12" s="157" t="n">
-        <v>2015</v>
+        <v>2027</v>
       </c>
       <c r="H12" s="157" t="n">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="I12" s="157" t="n">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="J12" s="157" t="n">
-        <v>2018</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="13">
@@ -14191,28 +14205,28 @@
         </is>
       </c>
       <c r="C13" s="39" t="n">
-        <v>40633</v>
+        <v>45291</v>
       </c>
       <c r="D13" s="39" t="n">
-        <v>40999</v>
+        <v>45657</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>41364</v>
+        <v>46022</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>41729</v>
+        <v>46387</v>
       </c>
       <c r="G13" s="39" t="n">
-        <v>42094</v>
+        <v>46752</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>42460</v>
+        <v>47118</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>42825</v>
+        <v>47483</v>
       </c>
       <c r="J13" s="39" t="n">
-        <v>43190</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="14">
@@ -14230,28 +14244,28 @@
         </is>
       </c>
       <c r="C15" s="162" t="n">
-        <v>843.6000000000003</v>
+        <v>340.1</v>
       </c>
       <c r="D15" s="162" t="n">
-        <v>906.4999999999999</v>
+        <v>183.1</v>
       </c>
       <c r="E15" s="162" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
       <c r="F15" s="162" t="n">
-        <v>947.6792413199889</v>
+        <v>359.6</v>
       </c>
       <c r="G15" s="162" t="n">
-        <v>1000.484484594448</v>
+        <v>398</v>
       </c>
       <c r="H15" s="162" t="n">
-        <v>1078.88768747765</v>
+        <v>439.4</v>
       </c>
       <c r="I15" s="162" t="n">
-        <v>1150.07160606407</v>
+        <v>464.4</v>
       </c>
       <c r="J15" s="162" t="n">
-        <v>1226.874119002437</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="16">
@@ -14261,28 +14275,28 @@
         </is>
       </c>
       <c r="C16" s="162" t="n">
-        <v>532.8000000000003</v>
+        <v>259.5</v>
       </c>
       <c r="D16" s="162" t="n">
-        <v>543.8999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E16" s="162" t="n">
-        <v>465.4000000000003</v>
+        <v>225.7</v>
       </c>
       <c r="F16" s="162" t="n">
-        <v>493.6803141804108</v>
+        <v>267.2</v>
       </c>
       <c r="G16" s="162" t="n">
-        <v>559.8040395999167</v>
+        <v>301</v>
       </c>
       <c r="H16" s="162" t="n">
-        <v>634.7919640514119</v>
+        <v>337.6</v>
       </c>
       <c r="I16" s="162" t="n">
-        <v>709.3122632461741</v>
+        <v>358.5</v>
       </c>
       <c r="J16" s="162" t="n">
-        <v>787.9602383046408</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="17">
@@ -14292,28 +14306,28 @@
         </is>
       </c>
       <c r="C17" s="514" t="n">
-        <v>0.1413514022209673</v>
+        <v>0.21</v>
       </c>
       <c r="D17" s="514" t="n">
-        <v>0.2433962264150944</v>
+        <v>0.21</v>
       </c>
       <c r="E17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="F17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="G17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="H17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="I17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="J17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="18">
@@ -14323,28 +14337,28 @@
         </is>
       </c>
       <c r="C18" s="71" t="n">
-        <v>457.4879728966689</v>
+        <v>205</v>
       </c>
       <c r="D18" s="71" t="n">
-        <v>411.51679245283</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E18" s="71" t="n">
-        <v>360.007945781725</v>
+        <v>178.3</v>
       </c>
       <c r="F18" s="71" t="n">
-        <v>381.8840476600047</v>
+        <v>211.1</v>
       </c>
       <c r="G18" s="71" t="n">
-        <v>433.0337394427961</v>
+        <v>237.8</v>
       </c>
       <c r="H18" s="71" t="n">
-        <v>491.0402900234106</v>
+        <v>266.7</v>
       </c>
       <c r="I18" s="71" t="n">
-        <v>548.6851113215323</v>
+        <v>283.2</v>
       </c>
       <c r="J18" s="71" t="n">
-        <v>609.522876557224</v>
+        <v>291.7</v>
       </c>
     </row>
     <row r="19">
@@ -14659,7 +14673,7 @@
         </is>
       </c>
       <c r="J36" s="140" t="n">
-        <v>1226.874119002437</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="37">
@@ -14677,7 +14691,7 @@
         </is>
       </c>
       <c r="J37" s="412" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="K37" s="411" t="n"/>
     </row>
@@ -14804,7 +14818,7 @@
         </is>
       </c>
       <c r="C45" s="162" t="n">
-        <v>179.9999999999991</v>
+        <v>75</v>
       </c>
       <c r="H45" s="400" t="inlineStr">
         <is>
@@ -14829,7 +14843,7 @@
         </is>
       </c>
       <c r="C46" s="162" t="n">
-        <v>5190.276000000002</v>
+        <v>1572.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14851,7 +14865,7 @@
         </is>
       </c>
       <c r="C47" s="71" t="n">
-        <v>5010.276000000003</v>
+        <v>1497.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14875,7 +14889,7 @@
       <c r="F48" s="383" t="n"/>
       <c r="G48" s="383" t="n"/>
       <c r="H48" s="399" t="n">
-        <v>6741.92625</v>
+        <v>1574.8</v>
       </c>
       <c r="I48" s="57" t="n">
         <v>7372.933086845563</v>
@@ -14897,13 +14911,13 @@
         </is>
       </c>
       <c r="H49" s="512" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="I49" s="517" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="J49" s="517" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="50">
@@ -14913,7 +14927,7 @@
         </is>
       </c>
       <c r="C50" s="518" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E50" s="383" t="inlineStr">
         <is>
@@ -14921,7 +14935,7 @@
         </is>
       </c>
       <c r="H50" s="519" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
       <c r="I50" s="519" t="n">
         <v>50.57874302119625</v>
@@ -14937,7 +14951,7 @@
         </is>
       </c>
       <c r="C51" s="418" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="E51" s="100" t="inlineStr">
         <is>
@@ -14963,7 +14977,7 @@
         </is>
       </c>
       <c r="C52" s="140" t="n">
-        <v>5010.276000000003</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="53">
@@ -14973,7 +14987,7 @@
         </is>
       </c>
       <c r="C53" s="521" t="n">
-        <v>0.7748616857223557</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="55">
@@ -14983,7 +14997,7 @@
         </is>
       </c>
       <c r="C55" s="414" t="n">
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="56">
@@ -14993,7 +15007,7 @@
         </is>
       </c>
       <c r="C56" s="135" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="57">
@@ -15013,7 +15027,7 @@
         </is>
       </c>
       <c r="C58" s="418" t="n">
-        <v>0.2251383142776443</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="59">
@@ -15023,7 +15037,7 @@
         </is>
       </c>
       <c r="C59" s="418" t="n">
-        <v>0.06990222994664612</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="244" thickBot="1">
@@ -15691,7 +15705,7 @@
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Diluted shares for BMC</t>
+          <t>Diluted shares for ZoomInfo (GTM) — LBOMODEL1</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
@@ -15715,7 +15729,7 @@
         </is>
       </c>
       <c r="E5" s="496" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="6">
@@ -15725,7 +15739,7 @@
         </is>
       </c>
       <c r="E6" s="537" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="7">
@@ -15735,7 +15749,7 @@
         </is>
       </c>
       <c r="E7" s="505" t="n">
-        <v>143.973</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="8">
@@ -15745,7 +15759,7 @@
         </is>
       </c>
       <c r="E8" s="504" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15755,7 +15769,7 @@
         </is>
       </c>
       <c r="E9" s="444" t="n">
-        <v>411.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15765,7 +15779,7 @@
         </is>
       </c>
       <c r="E10" s="444" t="n">
-        <v>8.901621621621622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15775,7 +15789,7 @@
         </is>
       </c>
       <c r="E11" s="444" t="n">
-        <v>1.798378378378377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15800,7 +15814,7 @@
       </c>
       <c r="D14" s="417" t="n"/>
       <c r="E14" s="444" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="15">
@@ -15840,13 +15854,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="298" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="298" t="n">
         <v>15</v>
       </c>
       <c r="E18" s="299" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15854,13 +15868,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="298" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D19" s="298" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="299" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15868,13 +15882,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="298" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="298" t="n">
         <v>22</v>
       </c>
       <c r="E20" s="299" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15882,13 +15896,13 @@
         <v>4</v>
       </c>
       <c r="C21" s="298" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D21" s="298" t="n">
         <v>28</v>
       </c>
       <c r="E21" s="299" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -15896,13 +15910,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="298" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="298" t="n">
         <v>32</v>
       </c>
       <c r="E22" s="299" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15910,13 +15924,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="298" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D23" s="298" t="n">
         <v>36</v>
       </c>
       <c r="E23" s="299" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -15924,13 +15938,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="298" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="D24" s="298" t="n">
         <v>39</v>
       </c>
       <c r="E24" s="299" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -15938,20 +15952,22 @@
         <v>8</v>
       </c>
       <c r="C25" s="298" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="D25" s="298" t="n">
         <v>42</v>
       </c>
       <c r="E25" s="299" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="538" t="n">
         <v>9</v>
       </c>
-      <c r="C26" s="298" t="n"/>
+      <c r="C26" s="298" t="n">
+        <v>0</v>
+      </c>
       <c r="D26" s="298" t="n"/>
       <c r="E26" s="299" t="n">
         <v>0</v>
@@ -15961,7 +15977,9 @@
       <c r="B27" s="538" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="298" t="n"/>
+      <c r="C27" s="298" t="n">
+        <v>0</v>
+      </c>
       <c r="D27" s="298" t="n"/>
       <c r="E27" s="300" t="n">
         <v>0</v>
@@ -15969,7 +15987,7 @@
     </row>
     <row r="28">
       <c r="E28" s="301" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15996,7 +16014,7 @@
     <row r="2" ht="18" customHeight="1" s="244" thickBot="1">
       <c r="A2" s="101" t="inlineStr">
         <is>
-          <t>52 week high low</t>
+          <t>52 week high low — NOTE: tape still sample/legacy; LBOMODEL1 uses GTM $4.31 spot on LBO!D8</t>
         </is>
       </c>
       <c r="B2" s="93" t="n"/>

--- a/LBO_Complex_Template_IRR_MoM.xlsx
+++ b/LBO_Complex_Template_IRR_MoM.xlsx
@@ -7,20 +7,31 @@
   </bookViews>
   <sheets>
     <sheet name="Coversheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LBO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DCF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Shares" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="52wkHL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ZI_Cover" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ZI_01_10K_Source" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ZI_02_SM_Isolation" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ZI_03_Headcount_AI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ZI_04_EBITDA_Bridge" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ZI_05_Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="00_Assumptions_List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Assumptions_Coversheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assumptions_LBO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Assumptions_DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions_Shares" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions_52wkHL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Assumptions_ZI_01_10K_Source" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Assumptions_ZI_02_SM_Isolation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Assumptions_ZI_03_Headcount_AI" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Assumptions_ZI_04_EBITDA_Bridge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Assumptions_ZI_05_Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="LBO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DCF" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Shares" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="52wkHL" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ZI_Cover" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ZI_01_10K_Source" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ZI_02_SM_Isolation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ZI_03_Headcount_AI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ZI_04_EBITDA_Bridge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="ZI_05_Sensitivity" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId12"/>
-    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
   </externalReferences>
   <definedNames>
     <definedName name="CIQWBGuid" hidden="1">"a611639b-bab1-425e-aaa5-008c326fdfdb"</definedName>
@@ -60,6 +71,7 @@
     <definedName name="Products">[2]Array0!$B$5:$C$7</definedName>
     <definedName name="Rev">'[1]Forecast Drivers'!$E$25:$S$25</definedName>
     <definedName name="CIQWBGuid" localSheetId="0" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Assumptions_List'!$B$6:$J$57</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
@@ -150,7 +162,7 @@
     <numFmt numFmtId="243" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="244" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="105">
+  <fonts count="108">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -835,6 +847,22 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1766,7 +1794,7 @@
     <xf numFmtId="244" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="238" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="558">
+  <cellXfs count="561">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2746,6 +2774,15 @@
     <xf numFmtId="182" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="190" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="190" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4794,7 +4831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M45"/>
+  <dimension ref="B2:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -4861,16 +4898,30 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Assumptions list (all tabs): LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.md|.pdf</t>
+      <c r="B44" s="544" t="inlineStr">
+        <is>
+          <t>IN-WORKBOOK ASSUMPTIONS LIST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
+          <t>See sheet 00_Assumptions_List (all tabs) and Assumptions_* sheets (one per tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>51 assumptions · What / How / Why / Source · filterable on 00_Assumptions_List</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Also exported: LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf|.md|.csv</t>
         </is>
       </c>
     </row>
@@ -4890,304 +4941,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E25"/>
+  <dimension ref="B2:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="55" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>EBITDA margin expansion bridge (target ≥500 bps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 baseline Revenue ($m)</t>
-        </is>
-      </c>
-      <c r="C4" s="557">
-        <f>'ZI_01_10K_Source'!E5</f>
-        <v/>
+          <t>Assumptions — ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_03_Headcount_AI` only.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 GAAP EBITDA proxy ($m)</t>
-        </is>
-      </c>
-      <c r="C5" s="557">
-        <f>'ZI_01_10K_Source'!E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>Baseline EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C6" s="546">
-        <f>C5/C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Target margin expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C7" s="548" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>Required incremental EBITDA ($m)</t>
-        </is>
-      </c>
-      <c r="C8" s="557">
-        <f>C4*C7/10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="542" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C10" s="541" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="541" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E10" s="541" t="n">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="542" t="inlineStr">
-        <is>
-          <t>Revenue (flat case for margin math)</t>
-        </is>
-      </c>
-      <c r="C11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-      <c r="D11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-      <c r="E11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="542" t="inlineStr">
-        <is>
-          <t>Net EBITDA benefit from program</t>
-        </is>
-      </c>
-      <c r="C12" s="557">
-        <f>'ZI_03_Headcount_AI'!C39</f>
-        <v/>
-      </c>
-      <c r="D12" s="557">
-        <f>'ZI_03_Headcount_AI'!D39</f>
-        <v/>
-      </c>
-      <c r="E12" s="557">
-        <f>'ZI_03_Headcount_AI'!E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="542" t="inlineStr">
-        <is>
-          <t>Run-rate benefit (ex one-time)</t>
-        </is>
-      </c>
-      <c r="C13" s="557">
-        <f>'ZI_03_Headcount_AI'!C40</f>
-        <v/>
-      </c>
-      <c r="D13" s="557">
-        <f>'ZI_03_Headcount_AI'!D40</f>
-        <v/>
-      </c>
-      <c r="E13" s="557">
-        <f>'ZI_03_Headcount_AI'!E40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="542" t="inlineStr">
-        <is>
-          <t>Pro forma EBITDA</t>
-        </is>
-      </c>
-      <c r="C14" s="557">
-        <f>$C$5+C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="557">
-        <f>$C$5+D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="557">
-        <f>$C$5+E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="542" t="inlineStr">
-        <is>
-          <t>Pro forma EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C15" s="546">
-        <f>C14/C11</f>
-        <v/>
-      </c>
-      <c r="D15" s="546">
-        <f>D14/D11</f>
-        <v/>
-      </c>
-      <c r="E15" s="546">
-        <f>E14/E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="544" t="inlineStr">
-        <is>
-          <t>Margin expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C16" s="557">
-        <f>(C15-$C$6)*10000</f>
-        <v/>
-      </c>
-      <c r="D16" s="557">
-        <f>(D15-$C$6)*10000</f>
-        <v/>
-      </c>
-      <c r="E16" s="557">
-        <f>(E15-$C$6)*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="544" t="inlineStr">
-        <is>
-          <t>Run-rate expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C17" s="557">
-        <f>(C13/$C$4)*10000</f>
-        <v/>
-      </c>
-      <c r="D17" s="557">
-        <f>(D13/$C$4)*10000</f>
-        <v/>
-      </c>
-      <c r="E17" s="557">
-        <f>(E13/$C$4)*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="542" t="inlineStr">
-        <is>
-          <t>Hits ≥500 bps run-rate?</t>
-        </is>
-      </c>
-      <c r="C18" s="554">
-        <f>IF(C17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="D18" s="554">
-        <f>IF(D17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="E18" s="554">
-        <f>IF(E17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M % revenue bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="542" t="inlineStr">
-        <is>
-          <t>Baseline S&amp;M %</t>
-        </is>
-      </c>
-      <c r="C21" s="546">
-        <f>'ZI_02_SM_Isolation'!C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="542" t="inlineStr">
-        <is>
-          <t>PF S&amp;M $ (baseline − SDR save + AI/oversight)</t>
-        </is>
-      </c>
-      <c r="C22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!C34+'ZI_03_Headcount_AI'!C35+'ZI_03_Headcount_AI'!C36</f>
-        <v/>
-      </c>
-      <c r="D22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!D34+'ZI_03_Headcount_AI'!D35+'ZI_03_Headcount_AI'!D36</f>
-        <v/>
-      </c>
-      <c r="E22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!E34+'ZI_03_Headcount_AI'!E35+'ZI_03_Headcount_AI'!E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="542" t="inlineStr">
-        <is>
-          <t>PF S&amp;M % revenue</t>
-        </is>
-      </c>
-      <c r="C23" s="546">
-        <f>C22/$C$4</f>
-        <v/>
-      </c>
-      <c r="D23" s="546">
-        <f>D22/$C$4</f>
-        <v/>
-      </c>
-      <c r="E23" s="546">
-        <f>E22/$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Yellow cells on 03_Headcount_AI drive the bridge. Base case sized to clear 500 bps by Y3 run-rate: 40% of S&amp;M = outbound SDRs; 95% replaced; $155k/SDR vs $15k AI seat + oversight. 500 bps on $1,249.5m revenue needs ~$62.5m run-rate EBITDA.</t>
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>% of S&amp;M that are outbound SDR/BDR</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Share of S&amp;M headcount treated as AI-replaceable SDRs.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input × 1,370.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>10-K does not disclose SDR count — explicit model assumption.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Fully loaded cost / SDR / yr</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$155k</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Cash cost per outbound SDR.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Below blended residual S&amp;M $/employee (commissions/ads stay).</t>
+        </is>
+      </c>
+      <c r="I7" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>C13/C15</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>AI seat / oversight cost</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>$15k per seat; $150k per oversight FTE</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Replacement opex for AI agents + humans.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs; 1 oversight FTE / 20 seats.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Net savings must clear AI + oversight to hit margin target.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>C21:E21</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Cumulative % SDRs replaced</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>45% / 80% / 95% (2026–28)</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Headcount reduction schedule.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Yellow cumulative exit fractions.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Phased cut to avoid one-year cliff risk.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>C16/C17</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Severance / AI build</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>$25k per SDR; $8m Y1 build</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>One-time costs.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs in P&amp;L impact.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Hits in-year EBITDA but excluded from run-rate bps.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
         </is>
       </c>
     </row>
@@ -5202,295 +5221,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H20"/>
+  <dimension ref="B2:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" style="244" min="2" max="2"/>
-    <col width="10" customWidth="1" style="244" min="3" max="3"/>
-    <col width="10" customWidth="1" style="244" min="4" max="4"/>
-    <col width="10" customWidth="1" style="244" min="5" max="5"/>
-    <col width="10" customWidth="1" style="244" min="6" max="6"/>
-    <col width="10" customWidth="1" style="244" min="7" max="7"/>
-    <col width="10" customWidth="1" style="244" min="8" max="8"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>Sensitivity — Y3 run-rate margin expansion (bps)</t>
+          <t>Assumptions — ZI_04_EBITDA_Bridge</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rows = cumulative % SDRs replaced; Cols = AI $/seat-yr ($000s). Other inputs from 03_Headcount_AI.</t>
+          <t>Subset of 00_Assumptions_List for tab `ZI_04_EBITDA_Bridge` only.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>SDR0</t>
-        </is>
-      </c>
-      <c r="C5" s="549">
-        <f>'ZI_03_Headcount_AI'!C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>SDR cost $k</t>
-        </is>
-      </c>
-      <c r="C6" s="557">
-        <f>'ZI_03_Headcount_AI'!C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Seats/SDR</t>
-        </is>
-      </c>
-      <c r="C7" s="555">
-        <f>'ZI_03_Headcount_AI'!C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>Oversight $k</t>
-        </is>
-      </c>
-      <c r="C8" s="557">
-        <f>'ZI_03_Headcount_AI'!C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="542" t="inlineStr">
-        <is>
-          <t>Revenue $m</t>
-        </is>
-      </c>
-      <c r="C9" s="557">
-        <f>'ZI_01_10K_Source'!E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>bps \ AI $k</t>
-        </is>
-      </c>
-      <c r="C11" s="548" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="548" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="548" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11" s="548" t="n">
-        <v>24</v>
-      </c>
-      <c r="G11" s="548" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="548" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="553" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*8/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*12/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*18/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*24/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*30/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*40/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="553" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*8/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*12/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*18/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*24/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*30/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*40/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="553" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*8/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*12/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*18/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*24/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*30/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*40/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="553" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*8/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*12/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*18/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*24/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*30/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*40/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="553" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*8/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*12/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*18/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*24/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*30/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*40/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="553" t="n">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*8/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*12/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*18/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*24/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*30/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*40/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="542" t="inlineStr">
-        <is>
-          <t>Base case Y3 run-rate bps (from bridge)</t>
-        </is>
-      </c>
-      <c r="C20" s="557">
-        <f>'ZI_04_EBITDA_Bridge'!E17</f>
-        <v/>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Target margin expansion</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>500 bps</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Minimum success hurdle for the AI program.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input; YES/NO vs run-rate bps.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> equates to ~$62.5m EBITDA on $1,249.5m revenue.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>User thesis requirement</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5498,7 +5335,127 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — ZI_05_Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_05_Sensitivity` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>B12:H17</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Sensitivity grid</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>Replace-% × AI $/seat → bps</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Y3 run-rate bps under alternate AI costs / cut depths.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Algebra on SDR0 &amp; unit costs.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Shows what it takes to stay above 500 bps if AI is more expensive.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Derived from ZI_03 inputs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14057,7 +14014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15687,7 +15644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15996,7 +15953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21300,7 +21257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21469,7 +21426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21949,7 +21906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22126,7 +22083,2415 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="22" customWidth="1" style="244" min="3" max="3"/>
+    <col width="14" customWidth="1" style="244" min="4" max="4"/>
+    <col width="32" customWidth="1" style="244" min="5" max="5"/>
+    <col width="28" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="36" customWidth="1" style="244" min="8" max="8"/>
+    <col width="40" customWidth="1" style="244" min="9" max="9"/>
+    <col width="55" customWidth="1" style="244" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — Assumptions List (every tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plain in-workbook list. Every row: Tab · Cell · Name · Value · What · How · Why · Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ticker: GTM (ZoomInfo Technologies Inc.). Educational / research use only — not investment advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="244">
+      <c r="B6" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C6" s="558" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="D6" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="E6" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="F6" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G6" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="H6" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="I6" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="J6" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>Coversheet</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>Model identity</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo (GTM)</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Name of this LBO case.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Set on Coversheet and LBO!B2.</t>
+        </is>
+      </c>
+      <c r="I7" s="559" t="inlineStr">
+        <is>
+          <t>Separates ZoomInfo LBOMODEL1 from the blank WSP BMC sample.</t>
+        </is>
+      </c>
+      <c r="J7" s="560" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/vengeanceaiUSC_LBOMODEL1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>Coversheet</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>$ millions except per share / rates / multiples</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Unit convention for the workbook.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Stated on LBO!B3 / DCF!B3.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Matches WSP template convention and SEC $ presentation scaled to millions.</t>
+        </is>
+      </c>
+      <c r="J8" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>D6/D7</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>Company / ticker</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc. / GTM</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Target company identity.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded inputs on LBO general inputs.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Public GTM (legacy ZI) is the LBOMODEL1 case company.</t>
+        </is>
+      </c>
+      <c r="J9" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>$4.31</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Spot equity price used for premium math.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D8 market input.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Latest available GTM print used when MODEL1 was built (~2026-08-12).</t>
+        </is>
+      </c>
+      <c r="J10" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>Price date</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>As-of date for the spot price.</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D9.</t>
+        </is>
+      </c>
+      <c r="I11" s="559" t="inlineStr">
+        <is>
+          <t>Timestamps the market input for auditability.</t>
+        </is>
+      </c>
+      <c r="J11" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>H21</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>Acquisition premium</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Premium of offer price over spot.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh = D8×(1+premium).</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>Standard illustrative take-private premium; editable deal assumption.</t>
+        </is>
+      </c>
+      <c r="J12" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>H20</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>Offer price / share</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>Implied takeout price per share.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>D8 × 1.25.</t>
+        </is>
+      </c>
+      <c r="I13" s="559" t="inlineStr">
+        <is>
+          <t>Drives equity purchase price in Uses.</t>
+        </is>
+      </c>
+      <c r="J13" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption + market price</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>Diluted shares (millions)</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>292.312</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>Share count for equity value.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>From latest shares outstanding.</t>
+        </is>
+      </c>
+      <c r="I14" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30 common shares outstanding used as diluted proxy (options ladder not fully modeled).</t>
+        </is>
+      </c>
+      <c r="J14" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="244">
+      <c r="B15" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D15" s="559" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="E15" s="559" t="inlineStr">
+        <is>
+          <t>Equity purchase price</t>
+        </is>
+      </c>
+      <c r="F15" s="559" t="inlineStr">
+        <is>
+          <t>$1,574.8m</t>
+        </is>
+      </c>
+      <c r="G15" s="559" t="inlineStr">
+        <is>
+          <t>Cash to buy equity.</t>
+        </is>
+      </c>
+      <c r="H15" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh × shares.</t>
+        </is>
+      </c>
+      <c r="I15" s="559" t="inlineStr">
+        <is>
+          <t>Primary Use of funds line.</t>
+        </is>
+      </c>
+      <c r="J15" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="244">
+      <c r="B16" s="559" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D16" s="559" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="E16" s="559" t="inlineStr">
+        <is>
+          <t>LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="F16" s="559" t="inlineStr">
+        <is>
+          <t>$314.5m</t>
+        </is>
+      </c>
+      <c r="G16" s="559" t="inlineStr">
+        <is>
+          <t>Entry EBITDA for leverage / multiple math.</t>
+        </is>
+      </c>
+      <c r="H16" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 OpInc $225.7m + D&amp;A $88.8m.</t>
+        </is>
+      </c>
+      <c r="I16" s="559" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA proxy from latest annual 10-K (not adjusted EBITDA).</t>
+        </is>
+      </c>
+      <c r="J16" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="244">
+      <c r="B17" s="559" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D17" s="559" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="E17" s="559" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="F17" s="559" t="inlineStr">
+        <is>
+          <t>−$1,269.9m</t>
+        </is>
+      </c>
+      <c r="G17" s="559" t="inlineStr">
+        <is>
+          <t>Debt refinanced at close (entered as negative in template).</t>
+        </is>
+      </c>
+      <c r="H17" s="559" t="inlineStr">
+        <is>
+          <t>LT debt + current maturities.</t>
+        </is>
+      </c>
+      <c r="I17" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30: LongTermDebt + LongTermDebtCurrent.</t>
+        </is>
+      </c>
+      <c r="J17" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="244">
+      <c r="B18" s="559" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D18" s="559" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="E18" s="559" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F18" s="559" t="inlineStr">
+        <is>
+          <t>$150.1m</t>
+        </is>
+      </c>
+      <c r="G18" s="559" t="inlineStr">
+        <is>
+          <t>Cash available at entry.</t>
+        </is>
+      </c>
+      <c r="H18" s="559" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents + short-term investments.</t>
+        </is>
+      </c>
+      <c r="I18" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30.</t>
+        </is>
+      </c>
+      <c r="J18" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="244">
+      <c r="B19" s="559" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D19" s="559" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="E19" s="559" t="inlineStr">
+        <is>
+          <t>Minimum cash</t>
+        </is>
+      </c>
+      <c r="F19" s="559" t="inlineStr">
+        <is>
+          <t>$50.0m</t>
+        </is>
+      </c>
+      <c r="G19" s="559" t="inlineStr">
+        <is>
+          <t>Cash retained for ops; excess used as a Source.</t>
+        </is>
+      </c>
+      <c r="H19" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy input.</t>
+        </is>
+      </c>
+      <c r="I19" s="559" t="inlineStr">
+        <is>
+          <t>Leaves liquidity post-close; excess cash = 150.1 − 50 = 100.1.</t>
+        </is>
+      </c>
+      <c r="J19" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="244">
+      <c r="B20" s="559" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D20" s="559" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="E20" s="559" t="inlineStr">
+        <is>
+          <t>Entry EV / LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="F20" s="559" t="inlineStr">
+        <is>
+          <t>8.57x</t>
+        </is>
+      </c>
+      <c r="G20" s="559" t="inlineStr">
+        <is>
+          <t>Implied entry multiple.</t>
+        </is>
+      </c>
+      <c r="H20" s="559" t="inlineStr">
+        <is>
+          <t>(Equity buy + debt − cash) / EBITDA.</t>
+        </is>
+      </c>
+      <c r="I20" s="559" t="inlineStr">
+        <is>
+          <t>Output of offer + net debt vs LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="J20" s="559" t="inlineStr">
+        <is>
+          <t>Derived from SEC + market inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="244">
+      <c r="B21" s="559" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D21" s="559" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="E21" s="559" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="F21" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="G21" s="559" t="inlineStr">
+        <is>
+          <t>Exit multiple in hold-year 5.</t>
+        </is>
+      </c>
+      <c r="H21" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17 policy input.</t>
+        </is>
+      </c>
+      <c r="I21" s="559" t="inlineStr">
+        <is>
+          <t>Near entry; assumes modest multiple compression vs entry 8.57x.</t>
+        </is>
+      </c>
+      <c r="J21" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="244">
+      <c r="B22" s="559" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D22" s="559" t="inlineStr">
+        <is>
+          <t>C29/D29</t>
+        </is>
+      </c>
+      <c r="E22" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan A</t>
+        </is>
+      </c>
+      <c r="F22" s="559" t="inlineStr">
+        <is>
+          <t>2.5x / $786.2m</t>
+        </is>
+      </c>
+      <c r="G22" s="559" t="inlineStr">
+        <is>
+          <t>New TLA quantum.</t>
+        </is>
+      </c>
+      <c r="H22" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I22" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="J22" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="244">
+      <c r="B23" s="559" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D23" s="559" t="inlineStr">
+        <is>
+          <t>C30/D30</t>
+        </is>
+      </c>
+      <c r="E23" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan B</t>
+        </is>
+      </c>
+      <c r="F23" s="559" t="inlineStr">
+        <is>
+          <t>1.5x / $471.8m</t>
+        </is>
+      </c>
+      <c r="G23" s="559" t="inlineStr">
+        <is>
+          <t>New TLB quantum.</t>
+        </is>
+      </c>
+      <c r="H23" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I23" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="J23" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="244">
+      <c r="B24" s="559" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D24" s="559" t="inlineStr">
+        <is>
+          <t>C31/D31</t>
+        </is>
+      </c>
+      <c r="E24" s="559" t="inlineStr">
+        <is>
+          <t>Senior Notes</t>
+        </is>
+      </c>
+      <c r="F24" s="559" t="inlineStr">
+        <is>
+          <t>1.0x / $314.5m</t>
+        </is>
+      </c>
+      <c r="G24" s="559" t="inlineStr">
+        <is>
+          <t>New senior notes quantum.</t>
+        </is>
+      </c>
+      <c r="H24" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I24" s="559" t="inlineStr">
+        <is>
+          <t>Completes 5.0x new debt with TLA+TLB.</t>
+        </is>
+      </c>
+      <c r="J24" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="244">
+      <c r="B25" s="559" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D25" s="559" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="E25" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor equity</t>
+        </is>
+      </c>
+      <c r="F25" s="559" t="inlineStr">
+        <is>
+          <t>$1,203.6m</t>
+        </is>
+      </c>
+      <c r="G25" s="559" t="inlineStr">
+        <is>
+          <t>Equity check (Sources plug).</t>
+        </is>
+      </c>
+      <c r="H25" s="559" t="inlineStr">
+        <is>
+          <t>Total Uses − excess cash − new debt.</t>
+        </is>
+      </c>
+      <c r="I25" s="559" t="inlineStr">
+        <is>
+          <t>Balancing figure so Sources = Uses ($2,876.2m).</t>
+        </is>
+      </c>
+      <c r="J25" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="244">
+      <c r="B26" s="559" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D26" s="559" t="inlineStr">
+        <is>
+          <t>G36</t>
+        </is>
+      </c>
+      <c r="E26" s="559" t="inlineStr">
+        <is>
+          <t>Transaction fee %</t>
+        </is>
+      </c>
+      <c r="F26" s="559" t="inlineStr">
+        <is>
+          <t>2% of equity value</t>
+        </is>
+      </c>
+      <c r="G26" s="559" t="inlineStr">
+        <is>
+          <t>M&amp;A / financing fee assumption.</t>
+        </is>
+      </c>
+      <c r="H26" s="559" t="inlineStr">
+        <is>
+          <t>Fees $ = 2% × equity purchase.</t>
+        </is>
+      </c>
+      <c r="I26" s="559" t="inlineStr">
+        <is>
+          <t>Simple fee load for Uses; financing fee dollars also shown in fee block.</t>
+        </is>
+      </c>
+      <c r="J26" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="244">
+      <c r="B27" s="559" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D27" s="559" t="inlineStr">
+        <is>
+          <t>F65:J65</t>
+        </is>
+      </c>
+      <c r="E27" s="559" t="inlineStr">
+        <is>
+          <t>Revenue growth (FY26–30)</t>
+        </is>
+      </c>
+      <c r="F27" s="559" t="inlineStr">
+        <is>
+          <t>4% / 5% / 5% / 4% / 3%</t>
+        </is>
+      </c>
+      <c r="G27" s="559" t="inlineStr">
+        <is>
+          <t>YoY revenue growth in forecast.</t>
+        </is>
+      </c>
+      <c r="H27" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded on growth row.</t>
+        </is>
+      </c>
+      <c r="I27" s="559" t="inlineStr">
+        <is>
+          <t>Modest recovery vs FY24 dip; not a hyper-growth case.</t>
+        </is>
+      </c>
+      <c r="J27" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="244">
+      <c r="B28" s="559" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D28" s="559" t="inlineStr">
+        <is>
+          <t>E66/F66</t>
+        </is>
+      </c>
+      <c r="E28" s="559" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="F28" s="559" t="inlineStr">
+        <is>
+          <t>FY25 82.35% → Fcst 82.85%</t>
+        </is>
+      </c>
+      <c r="G28" s="559" t="inlineStr">
+        <is>
+          <t>Gross profit % of sales.</t>
+        </is>
+      </c>
+      <c r="H28" s="559" t="inlineStr">
+        <is>
+          <t>From FY25 COGS implied by 10-K; slight +50 bps in forecast.</t>
+        </is>
+      </c>
+      <c r="I28" s="559" t="inlineStr">
+        <is>
+          <t>Software gross margin structure from SEC P&amp;L.</t>
+        </is>
+      </c>
+      <c r="J28" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="244">
+      <c r="B29" s="559" t="n">
+        <v>23</v>
+      </c>
+      <c r="C29" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D29" s="559" t="inlineStr">
+        <is>
+          <t>E67/F67</t>
+        </is>
+      </c>
+      <c r="E29" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D margin</t>
+        </is>
+      </c>
+      <c r="F29" s="559" t="inlineStr">
+        <is>
+          <t>14.57% flat in forecast</t>
+        </is>
+      </c>
+      <c r="G29" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D % of sales.</t>
+        </is>
+      </c>
+      <c r="H29" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 R&amp;D / Revenue held flat.</t>
+        </is>
+      </c>
+      <c r="I29" s="559" t="inlineStr">
+        <is>
+          <t>Keeps product investment while S&amp;M is the efficiency lever.</t>
+        </is>
+      </c>
+      <c r="J29" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1" s="244">
+      <c r="B30" s="559" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D30" s="559" t="inlineStr">
+        <is>
+          <t>F68:J68</t>
+        </is>
+      </c>
+      <c r="E30" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A margin path</t>
+        </is>
+      </c>
+      <c r="F30" s="559" t="inlineStr">
+        <is>
+          <t>47.72% → 46.22% → 44.72% → 44.22% → 44.22%</t>
+        </is>
+      </c>
+      <c r="G30" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A (S&amp;M+G&amp;A) % of sales in forecast.</t>
+        </is>
+      </c>
+      <c r="H30" s="559" t="inlineStr">
+        <is>
+          <t>Compresses ~500 bps of revenue by Y3 vs FY25 49.72%.</t>
+        </is>
+      </c>
+      <c r="I30" s="559" t="inlineStr">
+        <is>
+          <t>Operationalizes ZI AI-SDR thesis into the LBO P&amp;L.</t>
+        </is>
+      </c>
+      <c r="J30" s="559" t="inlineStr">
+        <is>
+          <t>LBOMODEL1 thesis + ZI_* tabs; FY25 base from https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" s="244">
+      <c r="B31" s="559" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D31" s="559" t="inlineStr">
+        <is>
+          <t>C69:J69</t>
+        </is>
+      </c>
+      <c r="E31" s="559" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="F31" s="559" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="G31" s="559" t="inlineStr">
+        <is>
+          <t>Book tax rate on EBT.</t>
+        </is>
+      </c>
+      <c r="H31" s="559" t="inlineStr">
+        <is>
+          <t>Flat statutory-like rate in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I31" s="559" t="inlineStr">
+        <is>
+          <t>Simplifies vs actual cash tax / NOL complexity.</t>
+        </is>
+      </c>
+      <c r="J31" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1" s="244">
+      <c r="B32" s="559" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D32" s="559" t="inlineStr">
+        <is>
+          <t>I275/J275</t>
+        </is>
+      </c>
+      <c r="E32" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor MoIC / IRR</t>
+        </is>
+      </c>
+      <c r="F32" s="559" t="inlineStr">
+        <is>
+          <t>~2.97x / ~24.4%</t>
+        </is>
+      </c>
+      <c r="G32" s="559" t="inlineStr">
+        <is>
+          <t>Base returns at 8.0x exit.</t>
+        </is>
+      </c>
+      <c r="H32" s="559" t="inlineStr">
+        <is>
+          <t>Exit equity / sponsor equity; IRR = MoIC^(1/5)−1.</t>
+        </is>
+      </c>
+      <c r="I32" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative; sensitive to exit multiple, leverage, and SG&amp;A path.</t>
+        </is>
+      </c>
+      <c r="J32" s="559" t="inlineStr">
+        <is>
+          <t>Derived on LBO returns block</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1" s="244">
+      <c r="B33" s="559" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D33" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E33" s="559" t="inlineStr">
+        <is>
+          <t>DCF reference share price</t>
+        </is>
+      </c>
+      <c r="F33" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875 (LBO offer)</t>
+        </is>
+      </c>
+      <c r="G33" s="559" t="inlineStr">
+        <is>
+          <t>Price shown in DCF header for football-field compare.</t>
+        </is>
+      </c>
+      <c r="H33" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer/sh.</t>
+        </is>
+      </c>
+      <c r="I33" s="559" t="inlineStr">
+        <is>
+          <t>Makes DCF tab speak the same deal price as the LBO.</t>
+        </is>
+      </c>
+      <c r="J33" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" s="244">
+      <c r="B34" s="559" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D34" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="E34" s="559" t="inlineStr">
+        <is>
+          <t>Basic / diluted share count</t>
+        </is>
+      </c>
+      <c r="F34" s="559" t="inlineStr">
+        <is>
+          <t>292.312m</t>
+        </is>
+      </c>
+      <c r="G34" s="559" t="inlineStr">
+        <is>
+          <t>Share count for per-share value.</t>
+        </is>
+      </c>
+      <c r="H34" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO shares.</t>
+        </is>
+      </c>
+      <c r="I34" s="559" t="inlineStr">
+        <is>
+          <t>Same 10-Q share count as LBO.</t>
+        </is>
+      </c>
+      <c r="J34" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1" s="244">
+      <c r="B35" s="559" t="n">
+        <v>29</v>
+      </c>
+      <c r="C35" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D35" s="559" t="inlineStr">
+        <is>
+          <t>C55/C56/C57</t>
+        </is>
+      </c>
+      <c r="E35" s="559" t="inlineStr">
+        <is>
+          <t>CAPM inputs</t>
+        </is>
+      </c>
+      <c r="F35" s="559" t="inlineStr">
+        <is>
+          <t>Rf 4.3% / β 1.20 / ERP 5.0%</t>
+        </is>
+      </c>
+      <c r="G35" s="559" t="inlineStr">
+        <is>
+          <t>Building blocks of cost of equity.</t>
+        </is>
+      </c>
+      <c r="H35" s="559" t="inlineStr">
+        <is>
+          <t>Ke = Rf + β×ERP.</t>
+        </is>
+      </c>
+      <c r="I35" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative SaaS CAPM stack for DCF tab (not Yacktman-adjusted).</t>
+        </is>
+      </c>
+      <c r="J35" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1" s="244">
+      <c r="B36" s="559" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D36" s="559" t="inlineStr">
+        <is>
+          <t>C50/C51</t>
+        </is>
+      </c>
+      <c r="E36" s="559" t="inlineStr">
+        <is>
+          <t>Cost of debt / tax</t>
+        </is>
+      </c>
+      <c r="F36" s="559" t="inlineStr">
+        <is>
+          <t>7.0% / 21%</t>
+        </is>
+      </c>
+      <c r="G36" s="559" t="inlineStr">
+        <is>
+          <t>After-tax debt cost inputs.</t>
+        </is>
+      </c>
+      <c r="H36" s="559" t="inlineStr">
+        <is>
+          <t>Rd×(1−t) in WACC.</t>
+        </is>
+      </c>
+      <c r="I36" s="559" t="inlineStr">
+        <is>
+          <t>Rounded financing cost vs new LBO stack.</t>
+        </is>
+      </c>
+      <c r="J36" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" s="244">
+      <c r="B37" s="559" t="n">
+        <v>31</v>
+      </c>
+      <c r="C37" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D37" s="559" t="inlineStr">
+        <is>
+          <t>C53/C58</t>
+        </is>
+      </c>
+      <c r="E37" s="559" t="inlineStr">
+        <is>
+          <t>Capital structure weights</t>
+        </is>
+      </c>
+      <c r="F37" s="559" t="inlineStr">
+        <is>
+          <t>Wd 45% / We 55%</t>
+        </is>
+      </c>
+      <c r="G37" s="559" t="inlineStr">
+        <is>
+          <t>Target weights in WACC.</t>
+        </is>
+      </c>
+      <c r="H37" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy on DCF tab.</t>
+        </is>
+      </c>
+      <c r="I37" s="559" t="inlineStr">
+        <is>
+          <t>Closer to PF leveraged structure than pre-deal equity-heavy weights.</t>
+        </is>
+      </c>
+      <c r="J37" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1" s="244">
+      <c r="B38" s="559" t="n">
+        <v>32</v>
+      </c>
+      <c r="C38" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D38" s="559" t="inlineStr">
+        <is>
+          <t>C9/C59</t>
+        </is>
+      </c>
+      <c r="E38" s="559" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="F38" s="559" t="inlineStr">
+        <is>
+          <t>~8.53%</t>
+        </is>
+      </c>
+      <c r="G38" s="559" t="inlineStr">
+        <is>
+          <t>Discount rate for unlevered FCF.</t>
+        </is>
+      </c>
+      <c r="H38" s="559" t="inlineStr">
+        <is>
+          <t>We×Ke + Wd×Rd×(1−t).</t>
+        </is>
+      </c>
+      <c r="I38" s="559" t="inlineStr">
+        <is>
+          <t>Used for DCF PV math on this tab.</t>
+        </is>
+      </c>
+      <c r="J38" s="559" t="inlineStr">
+        <is>
+          <t>Derived from CAPM + Rd assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" s="244">
+      <c r="B39" s="559" t="n">
+        <v>33</v>
+      </c>
+      <c r="C39" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D39" s="559" t="inlineStr">
+        <is>
+          <t>J37</t>
+        </is>
+      </c>
+      <c r="E39" s="559" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple (DCF)</t>
+        </is>
+      </c>
+      <c r="F39" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="G39" s="559" t="inlineStr">
+        <is>
+          <t>Terminal multiple in exit-EBITDA approach.</t>
+        </is>
+      </c>
+      <c r="H39" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO!D17.</t>
+        </is>
+      </c>
+      <c r="I39" s="559" t="inlineStr">
+        <is>
+          <t>Keeps LBO and DCF exit frameworks comparable.</t>
+        </is>
+      </c>
+      <c r="J39" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" s="244">
+      <c r="B40" s="559" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D40" s="559" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="E40" s="559" t="inlineStr">
+        <is>
+          <t>Perpetuity g</t>
+        </is>
+      </c>
+      <c r="F40" s="559" t="inlineStr">
+        <is>
+          <t>0% in template cell (sensitivity uses 2–4%)</t>
+        </is>
+      </c>
+      <c r="G40" s="559" t="inlineStr">
+        <is>
+          <t>Long-term growth in Gordon approach.</t>
+        </is>
+      </c>
+      <c r="H40" s="559" t="inlineStr">
+        <is>
+          <t>Template default; grid varies g.</t>
+        </is>
+      </c>
+      <c r="I40" s="559" t="inlineStr">
+        <is>
+          <t>Football-field sensitivity still shows 2–4% g range.</t>
+        </is>
+      </c>
+      <c r="J40" s="559" t="inlineStr">
+        <is>
+          <t>WSP template convention + MODEL1 note</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" s="244">
+      <c r="B41" s="559" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D41" s="559" t="inlineStr">
+        <is>
+          <t>C31</t>
+        </is>
+      </c>
+      <c r="E41" s="559" t="inlineStr">
+        <is>
+          <t>Cash-flow timing</t>
+        </is>
+      </c>
+      <c r="F41" s="559" t="inlineStr">
+        <is>
+          <t>Middle of period</t>
+        </is>
+      </c>
+      <c r="G41" s="559" t="inlineStr">
+        <is>
+          <t>Mid-year discounting convention.</t>
+        </is>
+      </c>
+      <c r="H41" s="559" t="inlineStr">
+        <is>
+          <t>Midperiod adjustment factor on DCF tab.</t>
+        </is>
+      </c>
+      <c r="I41" s="559" t="inlineStr">
+        <is>
+          <t>Standard IB mid-year convention for annual FCFs.</t>
+        </is>
+      </c>
+      <c r="J41" s="559" t="inlineStr">
+        <is>
+          <t>WSP template</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" s="244">
+      <c r="B42" s="559" t="n">
+        <v>36</v>
+      </c>
+      <c r="C42" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D42" s="559" t="inlineStr">
+        <is>
+          <t>E5/E6</t>
+        </is>
+      </c>
+      <c r="E42" s="559" t="inlineStr">
+        <is>
+          <t>Offer price for dilution</t>
+        </is>
+      </c>
+      <c r="F42" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="G42" s="559" t="inlineStr">
+        <is>
+          <t>Price used in treasury-stock method.</t>
+        </is>
+      </c>
+      <c r="H42" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer.</t>
+        </is>
+      </c>
+      <c r="I42" s="559" t="inlineStr">
+        <is>
+          <t>Aligns diluted-share math with deal price.</t>
+        </is>
+      </c>
+      <c r="J42" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" s="244">
+      <c r="B43" s="559" t="n">
+        <v>37</v>
+      </c>
+      <c r="C43" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D43" s="559" t="inlineStr">
+        <is>
+          <t>E7/E14</t>
+        </is>
+      </c>
+      <c r="E43" s="559" t="inlineStr">
+        <is>
+          <t>Basic &amp; net diluted shares</t>
+        </is>
+      </c>
+      <c r="F43" s="559" t="inlineStr">
+        <is>
+          <t>292.312m / 292.312m</t>
+        </is>
+      </c>
+      <c r="G43" s="559" t="inlineStr">
+        <is>
+          <t>Share count used for equity value.</t>
+        </is>
+      </c>
+      <c r="H43" s="559" t="inlineStr">
+        <is>
+          <t>Outstanding shares; options set to 0 in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I43" s="559" t="inlineStr">
+        <is>
+          <t>10-Q share count; detailed options ladder not loaded (net dilutive options = 0).</t>
+        </is>
+      </c>
+      <c r="J43" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1" s="244">
+      <c r="B44" s="559" t="n">
+        <v>38</v>
+      </c>
+      <c r="C44" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D44" s="559" t="inlineStr">
+        <is>
+          <t>E8:E11</t>
+        </is>
+      </c>
+      <c r="E44" s="559" t="inlineStr">
+        <is>
+          <t>Options / other dilutives</t>
+        </is>
+      </c>
+      <c r="F44" s="559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="559" t="inlineStr">
+        <is>
+          <t>Incremental dilutive securities.</t>
+        </is>
+      </c>
+      <c r="H44" s="559" t="inlineStr">
+        <is>
+          <t>Cleared BMC ladder; set to zero pending full award rollforward.</t>
+        </is>
+      </c>
+      <c r="I44" s="559" t="inlineStr">
+        <is>
+          <t>Conservative vs overstating dilution without a current award table.</t>
+        </is>
+      </c>
+      <c r="J44" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1) — update from proxy/10-K award note when refined</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" s="244">
+      <c r="B45" s="559" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="559" t="inlineStr">
+        <is>
+          <t>52wkHL</t>
+        </is>
+      </c>
+      <c r="D45" s="559" t="inlineStr">
+        <is>
+          <t>E4/E5</t>
+        </is>
+      </c>
+      <c r="E45" s="559" t="inlineStr">
+        <is>
+          <t>52-week high / low</t>
+        </is>
+      </c>
+      <c r="F45" s="559" t="inlineStr">
+        <is>
+          <t>Legacy sample tape (not GTM)</t>
+        </is>
+      </c>
+      <c r="G45" s="559" t="inlineStr">
+        <is>
+          <t>Market range for football-field.</t>
+        </is>
+      </c>
+      <c r="H45" s="559" t="inlineStr">
+        <is>
+          <t>Still WSP BMC sample series in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I45" s="559" t="inlineStr">
+        <is>
+          <t>Not yet replaced with GTM price history; LBO uses spot $4.31 instead.</t>
+        </is>
+      </c>
+      <c r="J45" s="559" t="inlineStr">
+        <is>
+          <t>WSP sample residual — replace with GTM tape in MODEL2+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1" s="244">
+      <c r="B46" s="559" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D46" s="559" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="E46" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Revenue</t>
+        </is>
+      </c>
+      <c r="F46" s="559" t="inlineStr">
+        <is>
+          <t>$1,249.5m</t>
+        </is>
+      </c>
+      <c r="G46" s="559" t="inlineStr">
+        <is>
+          <t>Annual revenue anchor.</t>
+        </is>
+      </c>
+      <c r="H46" s="559" t="inlineStr">
+        <is>
+          <t>XBRL RevenueFromContractWithCustomerExcludingAssessedTax.</t>
+        </is>
+      </c>
+      <c r="I46" s="559" t="inlineStr">
+        <is>
+          <t>Latest annual 10-K fact.</t>
+        </is>
+      </c>
+      <c r="J46" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" s="244">
+      <c r="B47" s="559" t="n">
+        <v>41</v>
+      </c>
+      <c r="C47" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D47" s="559" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="E47" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Selling &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="F47" s="559" t="inlineStr">
+        <is>
+          <t>$414.6m</t>
+        </is>
+      </c>
+      <c r="G47" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M expense (the bloat line).</t>
+        </is>
+      </c>
+      <c r="H47" s="559" t="inlineStr">
+        <is>
+          <t>XBRL SellingAndMarketingExpense.</t>
+        </is>
+      </c>
+      <c r="I47" s="559" t="inlineStr">
+        <is>
+          <t>33.2% of FY25 revenue — thesis starting point.</t>
+        </is>
+      </c>
+      <c r="J47" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" s="244">
+      <c r="B48" s="559" t="n">
+        <v>42</v>
+      </c>
+      <c r="C48" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D48" s="559" t="inlineStr">
+        <is>
+          <t>E10/E13/E20</t>
+        </is>
+      </c>
+      <c r="E48" s="559" t="inlineStr">
+        <is>
+          <t>OpInc / D&amp;A / EBITDA proxy</t>
+        </is>
+      </c>
+      <c r="F48" s="559" t="inlineStr">
+        <is>
+          <t>$225.7 / $88.8 / $314.5m</t>
+        </is>
+      </c>
+      <c r="G48" s="559" t="inlineStr">
+        <is>
+          <t>Operating income, D&amp;A, EBITDA proxy.</t>
+        </is>
+      </c>
+      <c r="H48" s="559" t="inlineStr">
+        <is>
+          <t>OpInc + OtherDepreciationAndAmortization.</t>
+        </is>
+      </c>
+      <c r="I48" s="559" t="inlineStr">
+        <is>
+          <t>Bridges to LBO!D13 LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="J48" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" s="244">
+      <c r="B49" s="559" t="n">
+        <v>43</v>
+      </c>
+      <c r="C49" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D49" s="559" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="E49" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M employees</t>
+        </is>
+      </c>
+      <c r="F49" s="559" t="inlineStr">
+        <is>
+          <t>1,370</t>
+        </is>
+      </c>
+      <c r="G49" s="559" t="inlineStr">
+        <is>
+          <t>Headcount in sales &amp; marketing.</t>
+        </is>
+      </c>
+      <c r="H49" s="559" t="inlineStr">
+        <is>
+          <t>10-K Human Capital disclosure (3,180 total).</t>
+        </is>
+      </c>
+      <c r="I49" s="559" t="inlineStr">
+        <is>
+          <t>Denominator for SDR % assumption.</t>
+        </is>
+      </c>
+      <c r="J49" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1" s="244">
+      <c r="B50" s="559" t="n">
+        <v>44</v>
+      </c>
+      <c r="C50" s="559" t="inlineStr">
+        <is>
+          <t>ZI_02_SM_Isolation</t>
+        </is>
+      </c>
+      <c r="D50" s="559" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="E50" s="559" t="inlineStr">
+        <is>
+          <t>Target mature SaaS S&amp;M % rev</t>
+        </is>
+      </c>
+      <c r="F50" s="559" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G50" s="559" t="inlineStr">
+        <is>
+          <t>Benchmark efficient S&amp;M intensity.</t>
+        </is>
+      </c>
+      <c r="H50" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input vs FY25 33.2%.</t>
+        </is>
+      </c>
+      <c r="I50" s="559" t="inlineStr">
+        <is>
+          <t>Defines “bloat” dollars vs a mature SaaS target.</t>
+        </is>
+      </c>
+      <c r="J50" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" s="244">
+      <c r="B51" s="559" t="n">
+        <v>45</v>
+      </c>
+      <c r="C51" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D51" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E51" s="559" t="inlineStr">
+        <is>
+          <t>% of S&amp;M that are outbound SDR/BDR</t>
+        </is>
+      </c>
+      <c r="F51" s="559" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G51" s="559" t="inlineStr">
+        <is>
+          <t>Share of S&amp;M headcount treated as AI-replaceable SDRs.</t>
+        </is>
+      </c>
+      <c r="H51" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input × 1,370.</t>
+        </is>
+      </c>
+      <c r="I51" s="559" t="inlineStr">
+        <is>
+          <t>10-K does not disclose SDR count — explicit model assumption.</t>
+        </is>
+      </c>
+      <c r="J51" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1" s="244">
+      <c r="B52" s="559" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D52" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="E52" s="559" t="inlineStr">
+        <is>
+          <t>Fully loaded cost / SDR / yr</t>
+        </is>
+      </c>
+      <c r="F52" s="559" t="inlineStr">
+        <is>
+          <t>$155k</t>
+        </is>
+      </c>
+      <c r="G52" s="559" t="inlineStr">
+        <is>
+          <t>Cash cost per outbound SDR.</t>
+        </is>
+      </c>
+      <c r="H52" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input.</t>
+        </is>
+      </c>
+      <c r="I52" s="559" t="inlineStr">
+        <is>
+          <t>Below blended residual S&amp;M $/employee (commissions/ads stay).</t>
+        </is>
+      </c>
+      <c r="J52" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1" s="244">
+      <c r="B53" s="559" t="n">
+        <v>47</v>
+      </c>
+      <c r="C53" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D53" s="559" t="inlineStr">
+        <is>
+          <t>C13/C15</t>
+        </is>
+      </c>
+      <c r="E53" s="559" t="inlineStr">
+        <is>
+          <t>AI seat / oversight cost</t>
+        </is>
+      </c>
+      <c r="F53" s="559" t="inlineStr">
+        <is>
+          <t>$15k per seat; $150k per oversight FTE</t>
+        </is>
+      </c>
+      <c r="G53" s="559" t="inlineStr">
+        <is>
+          <t>Replacement opex for AI agents + humans.</t>
+        </is>
+      </c>
+      <c r="H53" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs; 1 oversight FTE / 20 seats.</t>
+        </is>
+      </c>
+      <c r="I53" s="559" t="inlineStr">
+        <is>
+          <t>Net savings must clear AI + oversight to hit margin target.</t>
+        </is>
+      </c>
+      <c r="J53" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1" s="244">
+      <c r="B54" s="559" t="n">
+        <v>48</v>
+      </c>
+      <c r="C54" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D54" s="559" t="inlineStr">
+        <is>
+          <t>C21:E21</t>
+        </is>
+      </c>
+      <c r="E54" s="559" t="inlineStr">
+        <is>
+          <t>Cumulative % SDRs replaced</t>
+        </is>
+      </c>
+      <c r="F54" s="559" t="inlineStr">
+        <is>
+          <t>45% / 80% / 95% (2026–28)</t>
+        </is>
+      </c>
+      <c r="G54" s="559" t="inlineStr">
+        <is>
+          <t>Headcount reduction schedule.</t>
+        </is>
+      </c>
+      <c r="H54" s="559" t="inlineStr">
+        <is>
+          <t>Yellow cumulative exit fractions.</t>
+        </is>
+      </c>
+      <c r="I54" s="559" t="inlineStr">
+        <is>
+          <t>Phased cut to avoid one-year cliff risk.</t>
+        </is>
+      </c>
+      <c r="J54" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1" s="244">
+      <c r="B55" s="559" t="n">
+        <v>49</v>
+      </c>
+      <c r="C55" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D55" s="559" t="inlineStr">
+        <is>
+          <t>C16/C17</t>
+        </is>
+      </c>
+      <c r="E55" s="559" t="inlineStr">
+        <is>
+          <t>Severance / AI build</t>
+        </is>
+      </c>
+      <c r="F55" s="559" t="inlineStr">
+        <is>
+          <t>$25k per SDR; $8m Y1 build</t>
+        </is>
+      </c>
+      <c r="G55" s="559" t="inlineStr">
+        <is>
+          <t>One-time costs.</t>
+        </is>
+      </c>
+      <c r="H55" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs in P&amp;L impact.</t>
+        </is>
+      </c>
+      <c r="I55" s="559" t="inlineStr">
+        <is>
+          <t>Hits in-year EBITDA but excluded from run-rate bps.</t>
+        </is>
+      </c>
+      <c r="J55" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1" s="244">
+      <c r="B56" s="559" t="n">
+        <v>50</v>
+      </c>
+      <c r="C56" s="559" t="inlineStr">
+        <is>
+          <t>ZI_04_EBITDA_Bridge</t>
+        </is>
+      </c>
+      <c r="D56" s="559" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E56" s="559" t="inlineStr">
+        <is>
+          <t>Target margin expansion</t>
+        </is>
+      </c>
+      <c r="F56" s="559" t="inlineStr">
+        <is>
+          <t>500 bps</t>
+        </is>
+      </c>
+      <c r="G56" s="559" t="inlineStr">
+        <is>
+          <t>Minimum success hurdle for the AI program.</t>
+        </is>
+      </c>
+      <c r="H56" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input; YES/NO vs run-rate bps.</t>
+        </is>
+      </c>
+      <c r="I56" s="559" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> equates to ~$62.5m EBITDA on $1,249.5m revenue.</t>
+        </is>
+      </c>
+      <c r="J56" s="559" t="inlineStr">
+        <is>
+          <t>User thesis requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1" s="244">
+      <c r="B57" s="559" t="n">
+        <v>51</v>
+      </c>
+      <c r="C57" s="559" t="inlineStr">
+        <is>
+          <t>ZI_05_Sensitivity</t>
+        </is>
+      </c>
+      <c r="D57" s="559" t="inlineStr">
+        <is>
+          <t>B12:H17</t>
+        </is>
+      </c>
+      <c r="E57" s="559" t="inlineStr">
+        <is>
+          <t>Sensitivity grid</t>
+        </is>
+      </c>
+      <c r="F57" s="559" t="inlineStr">
+        <is>
+          <t>Replace-% × AI $/seat → bps</t>
+        </is>
+      </c>
+      <c r="G57" s="559" t="inlineStr">
+        <is>
+          <t>Y3 run-rate bps under alternate AI costs / cut depths.</t>
+        </is>
+      </c>
+      <c r="H57" s="559" t="inlineStr">
+        <is>
+          <t>Algebra on SDR0 &amp; unit costs.</t>
+        </is>
+      </c>
+      <c r="I57" s="559" t="inlineStr">
+        <is>
+          <t>Shows what it takes to stay above 500 bps if AI is more expensive.</t>
+        </is>
+      </c>
+      <c r="J57" s="559" t="inlineStr">
+        <is>
+          <t>Derived from ZI_03 inputs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B6:J57"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId17"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22614,4 +24979,2965 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="55" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="12" customWidth="1" style="244" min="4" max="4"/>
+    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>EBITDA margin expansion bridge (target ≥500 bps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 baseline Revenue ($m)</t>
+        </is>
+      </c>
+      <c r="C4" s="557">
+        <f>'ZI_01_10K_Source'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 GAAP EBITDA proxy ($m)</t>
+        </is>
+      </c>
+      <c r="C5" s="557">
+        <f>'ZI_01_10K_Source'!E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>Baseline EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C6" s="546">
+        <f>C5/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Target margin expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C7" s="548" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>Required incremental EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C8" s="557">
+        <f>C4*C7/10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="542" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C10" s="541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="541" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E10" s="541" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="542" t="inlineStr">
+        <is>
+          <t>Revenue (flat case for margin math)</t>
+        </is>
+      </c>
+      <c r="C11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="D11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="E11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="542" t="inlineStr">
+        <is>
+          <t>Net EBITDA benefit from program</t>
+        </is>
+      </c>
+      <c r="C12" s="557">
+        <f>'ZI_03_Headcount_AI'!C39</f>
+        <v/>
+      </c>
+      <c r="D12" s="557">
+        <f>'ZI_03_Headcount_AI'!D39</f>
+        <v/>
+      </c>
+      <c r="E12" s="557">
+        <f>'ZI_03_Headcount_AI'!E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="542" t="inlineStr">
+        <is>
+          <t>Run-rate benefit (ex one-time)</t>
+        </is>
+      </c>
+      <c r="C13" s="557">
+        <f>'ZI_03_Headcount_AI'!C40</f>
+        <v/>
+      </c>
+      <c r="D13" s="557">
+        <f>'ZI_03_Headcount_AI'!D40</f>
+        <v/>
+      </c>
+      <c r="E13" s="557">
+        <f>'ZI_03_Headcount_AI'!E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="542" t="inlineStr">
+        <is>
+          <t>Pro forma EBITDA</t>
+        </is>
+      </c>
+      <c r="C14" s="557">
+        <f>$C$5+C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="557">
+        <f>$C$5+D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="557">
+        <f>$C$5+E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="542" t="inlineStr">
+        <is>
+          <t>Pro forma EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C15" s="546">
+        <f>C14/C11</f>
+        <v/>
+      </c>
+      <c r="D15" s="546">
+        <f>D14/D11</f>
+        <v/>
+      </c>
+      <c r="E15" s="546">
+        <f>E14/E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="544" t="inlineStr">
+        <is>
+          <t>Margin expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C16" s="557">
+        <f>(C15-$C$6)*10000</f>
+        <v/>
+      </c>
+      <c r="D16" s="557">
+        <f>(D15-$C$6)*10000</f>
+        <v/>
+      </c>
+      <c r="E16" s="557">
+        <f>(E15-$C$6)*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="544" t="inlineStr">
+        <is>
+          <t>Run-rate expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C17" s="557">
+        <f>(C13/$C$4)*10000</f>
+        <v/>
+      </c>
+      <c r="D17" s="557">
+        <f>(D13/$C$4)*10000</f>
+        <v/>
+      </c>
+      <c r="E17" s="557">
+        <f>(E13/$C$4)*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="542" t="inlineStr">
+        <is>
+          <t>Hits ≥500 bps run-rate?</t>
+        </is>
+      </c>
+      <c r="C18" s="554">
+        <f>IF(C17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="D18" s="554">
+        <f>IF(D17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="E18" s="554">
+        <f>IF(E17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M % revenue bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="542" t="inlineStr">
+        <is>
+          <t>Baseline S&amp;M %</t>
+        </is>
+      </c>
+      <c r="C21" s="546">
+        <f>'ZI_02_SM_Isolation'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="542" t="inlineStr">
+        <is>
+          <t>PF S&amp;M $ (baseline − SDR save + AI/oversight)</t>
+        </is>
+      </c>
+      <c r="C22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!C34+'ZI_03_Headcount_AI'!C35+'ZI_03_Headcount_AI'!C36</f>
+        <v/>
+      </c>
+      <c r="D22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!D34+'ZI_03_Headcount_AI'!D35+'ZI_03_Headcount_AI'!D36</f>
+        <v/>
+      </c>
+      <c r="E22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!E34+'ZI_03_Headcount_AI'!E35+'ZI_03_Headcount_AI'!E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="542" t="inlineStr">
+        <is>
+          <t>PF S&amp;M % revenue</t>
+        </is>
+      </c>
+      <c r="C23" s="546">
+        <f>C22/$C$4</f>
+        <v/>
+      </c>
+      <c r="D23" s="546">
+        <f>D22/$C$4</f>
+        <v/>
+      </c>
+      <c r="E23" s="546">
+        <f>E22/$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yellow cells on 03_Headcount_AI drive the bridge. Base case sized to clear 500 bps by Y3 run-rate: 40% of S&amp;M = outbound SDRs; 95% replaced; $155k/SDR vs $15k AI seat + oversight. 500 bps on $1,249.5m revenue needs ~$62.5m run-rate EBITDA.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="18" customWidth="1" style="244" min="2" max="2"/>
+    <col width="10" customWidth="1" style="244" min="3" max="3"/>
+    <col width="10" customWidth="1" style="244" min="4" max="4"/>
+    <col width="10" customWidth="1" style="244" min="5" max="5"/>
+    <col width="10" customWidth="1" style="244" min="6" max="6"/>
+    <col width="10" customWidth="1" style="244" min="7" max="7"/>
+    <col width="10" customWidth="1" style="244" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Sensitivity — Y3 run-rate margin expansion (bps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rows = cumulative % SDRs replaced; Cols = AI $/seat-yr ($000s). Other inputs from 03_Headcount_AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>SDR0</t>
+        </is>
+      </c>
+      <c r="C5" s="549">
+        <f>'ZI_03_Headcount_AI'!C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>SDR cost $k</t>
+        </is>
+      </c>
+      <c r="C6" s="557">
+        <f>'ZI_03_Headcount_AI'!C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Seats/SDR</t>
+        </is>
+      </c>
+      <c r="C7" s="555">
+        <f>'ZI_03_Headcount_AI'!C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>Oversight $k</t>
+        </is>
+      </c>
+      <c r="C8" s="557">
+        <f>'ZI_03_Headcount_AI'!C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="542" t="inlineStr">
+        <is>
+          <t>Revenue $m</t>
+        </is>
+      </c>
+      <c r="C9" s="557">
+        <f>'ZI_01_10K_Source'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bps \ AI $k</t>
+        </is>
+      </c>
+      <c r="C11" s="548" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="548" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="548" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="548" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="548" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="548" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="553" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*8/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*12/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*18/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*24/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*30/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*40/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="553" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*8/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*12/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*18/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*24/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*30/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*40/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="553" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*8/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*12/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*18/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*24/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*30/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*40/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="553" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*8/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*12/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*18/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*24/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*30/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*40/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="553" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*8/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*12/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*18/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*24/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*30/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*40/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="553" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*8/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*12/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*18/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*24/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*30/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*40/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="542" t="inlineStr">
+        <is>
+          <t>Base case Y3 run-rate bps (from bridge)</t>
+        </is>
+      </c>
+      <c r="C20" s="557">
+        <f>'ZI_04_EBITDA_Bridge'!E17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — Coversheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `Coversheet` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Model identity</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo (GTM)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Name of this LBO case.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Set on Coversheet and LBO!B2.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Separates ZoomInfo LBOMODEL1 from the blank WSP BMC sample.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/vengeanceaiUSC_LBOMODEL1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$ millions except per share / rates / multiples</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Unit convention for the workbook.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Stated on LBO!B3 / DCF!B3.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Matches WSP template convention and SEC $ presentation scaled to millions.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — LBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `LBO` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>D6/D7</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Company / ticker</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc. / GTM</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Target company identity.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded inputs on LBO general inputs.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Public GTM (legacy ZI) is the LBOMODEL1 case company.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$4.31</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Spot equity price used for premium math.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D8 market input.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Latest available GTM print used when MODEL1 was built (~2026-08-12).</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>Price date</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>As-of date for the spot price.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D9.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Timestamps the market input for auditability.</t>
+        </is>
+      </c>
+      <c r="I8" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>H21</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Acquisition premium</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Premium of offer price over spot.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh = D8×(1+premium).</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Standard illustrative take-private premium; editable deal assumption.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>H20</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Offer price / share</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>Implied takeout price per share.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>D8 × 1.25.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Drives equity purchase price in Uses.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption + market price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>Diluted shares (millions)</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>292.312</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>Share count for equity value.</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>From latest shares outstanding.</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30 common shares outstanding used as diluted proxy (options ladder not fully modeled).</t>
+        </is>
+      </c>
+      <c r="I11" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>Equity purchase price</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>$1,574.8m</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>Cash to buy equity.</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh × shares.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Primary Use of funds line.</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>$314.5m</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>Entry EBITDA for leverage / multiple math.</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 OpInc $225.7m + D&amp;A $88.8m.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA proxy from latest annual 10-K (not adjusted EBITDA).</t>
+        </is>
+      </c>
+      <c r="I13" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>−$1,269.9m</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>Debt refinanced at close (entered as negative in template).</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>LT debt + current maturities.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30: LongTermDebt + LongTermDebtCurrent.</t>
+        </is>
+      </c>
+      <c r="I14" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="244">
+      <c r="B15" s="559" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="559" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="D15" s="559" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E15" s="559" t="inlineStr">
+        <is>
+          <t>$150.1m</t>
+        </is>
+      </c>
+      <c r="F15" s="559" t="inlineStr">
+        <is>
+          <t>Cash available at entry.</t>
+        </is>
+      </c>
+      <c r="G15" s="559" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents + short-term investments.</t>
+        </is>
+      </c>
+      <c r="H15" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30.</t>
+        </is>
+      </c>
+      <c r="I15" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="244">
+      <c r="B16" s="559" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="559" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="D16" s="559" t="inlineStr">
+        <is>
+          <t>Minimum cash</t>
+        </is>
+      </c>
+      <c r="E16" s="559" t="inlineStr">
+        <is>
+          <t>$50.0m</t>
+        </is>
+      </c>
+      <c r="F16" s="559" t="inlineStr">
+        <is>
+          <t>Cash retained for ops; excess used as a Source.</t>
+        </is>
+      </c>
+      <c r="G16" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy input.</t>
+        </is>
+      </c>
+      <c r="H16" s="559" t="inlineStr">
+        <is>
+          <t>Leaves liquidity post-close; excess cash = 150.1 − 50 = 100.1.</t>
+        </is>
+      </c>
+      <c r="I16" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="244">
+      <c r="B17" s="559" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="559" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="D17" s="559" t="inlineStr">
+        <is>
+          <t>Entry EV / LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="E17" s="559" t="inlineStr">
+        <is>
+          <t>8.57x</t>
+        </is>
+      </c>
+      <c r="F17" s="559" t="inlineStr">
+        <is>
+          <t>Implied entry multiple.</t>
+        </is>
+      </c>
+      <c r="G17" s="559" t="inlineStr">
+        <is>
+          <t>(Equity buy + debt − cash) / EBITDA.</t>
+        </is>
+      </c>
+      <c r="H17" s="559" t="inlineStr">
+        <is>
+          <t>Output of offer + net debt vs LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="I17" s="559" t="inlineStr">
+        <is>
+          <t>Derived from SEC + market inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="244">
+      <c r="B18" s="559" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="559" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="D18" s="559" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="E18" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="F18" s="559" t="inlineStr">
+        <is>
+          <t>Exit multiple in hold-year 5.</t>
+        </is>
+      </c>
+      <c r="G18" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17 policy input.</t>
+        </is>
+      </c>
+      <c r="H18" s="559" t="inlineStr">
+        <is>
+          <t>Near entry; assumes modest multiple compression vs entry 8.57x.</t>
+        </is>
+      </c>
+      <c r="I18" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="244">
+      <c r="B19" s="559" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="559" t="inlineStr">
+        <is>
+          <t>C29/D29</t>
+        </is>
+      </c>
+      <c r="D19" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan A</t>
+        </is>
+      </c>
+      <c r="E19" s="559" t="inlineStr">
+        <is>
+          <t>2.5x / $786.2m</t>
+        </is>
+      </c>
+      <c r="F19" s="559" t="inlineStr">
+        <is>
+          <t>New TLA quantum.</t>
+        </is>
+      </c>
+      <c r="G19" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H19" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="I19" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="244">
+      <c r="B20" s="559" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="559" t="inlineStr">
+        <is>
+          <t>C30/D30</t>
+        </is>
+      </c>
+      <c r="D20" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan B</t>
+        </is>
+      </c>
+      <c r="E20" s="559" t="inlineStr">
+        <is>
+          <t>1.5x / $471.8m</t>
+        </is>
+      </c>
+      <c r="F20" s="559" t="inlineStr">
+        <is>
+          <t>New TLB quantum.</t>
+        </is>
+      </c>
+      <c r="G20" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H20" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="I20" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="244">
+      <c r="B21" s="559" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="559" t="inlineStr">
+        <is>
+          <t>C31/D31</t>
+        </is>
+      </c>
+      <c r="D21" s="559" t="inlineStr">
+        <is>
+          <t>Senior Notes</t>
+        </is>
+      </c>
+      <c r="E21" s="559" t="inlineStr">
+        <is>
+          <t>1.0x / $314.5m</t>
+        </is>
+      </c>
+      <c r="F21" s="559" t="inlineStr">
+        <is>
+          <t>New senior notes quantum.</t>
+        </is>
+      </c>
+      <c r="G21" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H21" s="559" t="inlineStr">
+        <is>
+          <t>Completes 5.0x new debt with TLA+TLB.</t>
+        </is>
+      </c>
+      <c r="I21" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="244">
+      <c r="B22" s="559" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="559" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="D22" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor equity</t>
+        </is>
+      </c>
+      <c r="E22" s="559" t="inlineStr">
+        <is>
+          <t>$1,203.6m</t>
+        </is>
+      </c>
+      <c r="F22" s="559" t="inlineStr">
+        <is>
+          <t>Equity check (Sources plug).</t>
+        </is>
+      </c>
+      <c r="G22" s="559" t="inlineStr">
+        <is>
+          <t>Total Uses − excess cash − new debt.</t>
+        </is>
+      </c>
+      <c r="H22" s="559" t="inlineStr">
+        <is>
+          <t>Balancing figure so Sources = Uses ($2,876.2m).</t>
+        </is>
+      </c>
+      <c r="I22" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="244">
+      <c r="B23" s="559" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="559" t="inlineStr">
+        <is>
+          <t>G36</t>
+        </is>
+      </c>
+      <c r="D23" s="559" t="inlineStr">
+        <is>
+          <t>Transaction fee %</t>
+        </is>
+      </c>
+      <c r="E23" s="559" t="inlineStr">
+        <is>
+          <t>2% of equity value</t>
+        </is>
+      </c>
+      <c r="F23" s="559" t="inlineStr">
+        <is>
+          <t>M&amp;A / financing fee assumption.</t>
+        </is>
+      </c>
+      <c r="G23" s="559" t="inlineStr">
+        <is>
+          <t>Fees $ = 2% × equity purchase.</t>
+        </is>
+      </c>
+      <c r="H23" s="559" t="inlineStr">
+        <is>
+          <t>Simple fee load for Uses; financing fee dollars also shown in fee block.</t>
+        </is>
+      </c>
+      <c r="I23" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="244">
+      <c r="B24" s="559" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="559" t="inlineStr">
+        <is>
+          <t>F65:J65</t>
+        </is>
+      </c>
+      <c r="D24" s="559" t="inlineStr">
+        <is>
+          <t>Revenue growth (FY26–30)</t>
+        </is>
+      </c>
+      <c r="E24" s="559" t="inlineStr">
+        <is>
+          <t>4% / 5% / 5% / 4% / 3%</t>
+        </is>
+      </c>
+      <c r="F24" s="559" t="inlineStr">
+        <is>
+          <t>YoY revenue growth in forecast.</t>
+        </is>
+      </c>
+      <c r="G24" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded on growth row.</t>
+        </is>
+      </c>
+      <c r="H24" s="559" t="inlineStr">
+        <is>
+          <t>Modest recovery vs FY24 dip; not a hyper-growth case.</t>
+        </is>
+      </c>
+      <c r="I24" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="244">
+      <c r="B25" s="559" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="559" t="inlineStr">
+        <is>
+          <t>E66/F66</t>
+        </is>
+      </c>
+      <c r="D25" s="559" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="E25" s="559" t="inlineStr">
+        <is>
+          <t>FY25 82.35% → Fcst 82.85%</t>
+        </is>
+      </c>
+      <c r="F25" s="559" t="inlineStr">
+        <is>
+          <t>Gross profit % of sales.</t>
+        </is>
+      </c>
+      <c r="G25" s="559" t="inlineStr">
+        <is>
+          <t>From FY25 COGS implied by 10-K; slight +50 bps in forecast.</t>
+        </is>
+      </c>
+      <c r="H25" s="559" t="inlineStr">
+        <is>
+          <t>Software gross margin structure from SEC P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I25" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="244">
+      <c r="B26" s="559" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="559" t="inlineStr">
+        <is>
+          <t>E67/F67</t>
+        </is>
+      </c>
+      <c r="D26" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D margin</t>
+        </is>
+      </c>
+      <c r="E26" s="559" t="inlineStr">
+        <is>
+          <t>14.57% flat in forecast</t>
+        </is>
+      </c>
+      <c r="F26" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D % of sales.</t>
+        </is>
+      </c>
+      <c r="G26" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 R&amp;D / Revenue held flat.</t>
+        </is>
+      </c>
+      <c r="H26" s="559" t="inlineStr">
+        <is>
+          <t>Keeps product investment while S&amp;M is the efficiency lever.</t>
+        </is>
+      </c>
+      <c r="I26" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="244">
+      <c r="B27" s="559" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="559" t="inlineStr">
+        <is>
+          <t>F68:J68</t>
+        </is>
+      </c>
+      <c r="D27" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A margin path</t>
+        </is>
+      </c>
+      <c r="E27" s="559" t="inlineStr">
+        <is>
+          <t>47.72% → 46.22% → 44.72% → 44.22% → 44.22%</t>
+        </is>
+      </c>
+      <c r="F27" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A (S&amp;M+G&amp;A) % of sales in forecast.</t>
+        </is>
+      </c>
+      <c r="G27" s="559" t="inlineStr">
+        <is>
+          <t>Compresses ~500 bps of revenue by Y3 vs FY25 49.72%.</t>
+        </is>
+      </c>
+      <c r="H27" s="559" t="inlineStr">
+        <is>
+          <t>Operationalizes ZI AI-SDR thesis into the LBO P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I27" s="559" t="inlineStr">
+        <is>
+          <t>LBOMODEL1 thesis + ZI_* tabs; FY25 base from https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="244">
+      <c r="B28" s="559" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="559" t="inlineStr">
+        <is>
+          <t>C69:J69</t>
+        </is>
+      </c>
+      <c r="D28" s="559" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="E28" s="559" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="F28" s="559" t="inlineStr">
+        <is>
+          <t>Book tax rate on EBT.</t>
+        </is>
+      </c>
+      <c r="G28" s="559" t="inlineStr">
+        <is>
+          <t>Flat statutory-like rate in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H28" s="559" t="inlineStr">
+        <is>
+          <t>Simplifies vs actual cash tax / NOL complexity.</t>
+        </is>
+      </c>
+      <c r="I28" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="244">
+      <c r="B29" s="559" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="559" t="inlineStr">
+        <is>
+          <t>I275/J275</t>
+        </is>
+      </c>
+      <c r="D29" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor MoIC / IRR</t>
+        </is>
+      </c>
+      <c r="E29" s="559" t="inlineStr">
+        <is>
+          <t>~2.97x / ~24.4%</t>
+        </is>
+      </c>
+      <c r="F29" s="559" t="inlineStr">
+        <is>
+          <t>Base returns at 8.0x exit.</t>
+        </is>
+      </c>
+      <c r="G29" s="559" t="inlineStr">
+        <is>
+          <t>Exit equity / sponsor equity; IRR = MoIC^(1/5)−1.</t>
+        </is>
+      </c>
+      <c r="H29" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative; sensitive to exit multiple, leverage, and SG&amp;A path.</t>
+        </is>
+      </c>
+      <c r="I29" s="559" t="inlineStr">
+        <is>
+          <t>Derived on LBO returns block</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — DCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `DCF` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>DCF reference share price</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875 (LBO offer)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Price shown in DCF header for football-field compare.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer/sh.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Makes DCF tab speak the same deal price as the LBO.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Basic / diluted share count</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>292.312m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Share count for per-share value.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO shares.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Same 10-Q share count as LBO.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>C55/C56/C57</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>CAPM inputs</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>Rf 4.3% / β 1.20 / ERP 5.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Building blocks of cost of equity.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Ke = Rf + β×ERP.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative SaaS CAPM stack for DCF tab (not Yacktman-adjusted).</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>C50/C51</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Cost of debt / tax</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>7.0% / 21%</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>After-tax debt cost inputs.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Rd×(1−t) in WACC.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Rounded financing cost vs new LBO stack.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>C53/C58</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Capital structure weights</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>Wd 45% / We 55%</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>Target weights in WACC.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy on DCF tab.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Closer to PF leveraged structure than pre-deal equity-heavy weights.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>C9/C59</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>~8.53%</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>Discount rate for unlevered FCF.</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>We×Ke + Wd×Rd×(1−t).</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>Used for DCF PV math on this tab.</t>
+        </is>
+      </c>
+      <c r="I11" s="559" t="inlineStr">
+        <is>
+          <t>Derived from CAPM + Rd assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>J37</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple (DCF)</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>Terminal multiple in exit-EBITDA approach.</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO!D17.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Keeps LBO and DCF exit frameworks comparable.</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>Perpetuity g</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>0% in template cell (sensitivity uses 2–4%)</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>Long-term growth in Gordon approach.</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>Template default; grid varies g.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>Football-field sensitivity still shows 2–4% g range.</t>
+        </is>
+      </c>
+      <c r="I13" s="559" t="inlineStr">
+        <is>
+          <t>WSP template convention + MODEL1 note</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>C31</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>Cash-flow timing</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>Middle of period</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>Mid-year discounting convention.</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>Midperiod adjustment factor on DCF tab.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>Standard IB mid-year convention for annual FCFs.</t>
+        </is>
+      </c>
+      <c r="I14" s="559" t="inlineStr">
+        <is>
+          <t>WSP template</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — Shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `Shares` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E5/E6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Offer price for dilution</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Price used in treasury-stock method.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Aligns diluted-share math with deal price.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>E7/E14</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Basic &amp; net diluted shares</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>292.312m / 292.312m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Share count used for equity value.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Outstanding shares; options set to 0 in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>10-Q share count; detailed options ladder not loaded (net dilutive options = 0).</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>E8:E11</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>Options / other dilutives</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Incremental dilutive securities.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Cleared BMC ladder; set to zero pending full award rollforward.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Conservative vs overstating dilution without a current award table.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1) — update from proxy/10-K award note when refined</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — 52wkHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `52wkHL` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E4/E5</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>52-week high / low</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>Legacy sample tape (not GTM)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Market range for football-field.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Still WSP BMC sample series in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Not yet replaced with GTM price history; LBO uses spot $4.31 instead.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>WSP sample residual — replace with GTM tape in MODEL2+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — ZI_01_10K_Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_01_10K_Source` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Revenue</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$1,249.5m</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Annual revenue anchor.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>XBRL RevenueFromContractWithCustomerExcludingAssessedTax.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Latest annual 10-K fact.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Selling &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$414.6m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M expense (the bloat line).</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>XBRL SellingAndMarketingExpense.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>33.2% of FY25 revenue — thesis starting point.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>E10/E13/E20</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>OpInc / D&amp;A / EBITDA proxy</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>$225.7 / $88.8 / $314.5m</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Operating income, D&amp;A, EBITDA proxy.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>OpInc + OtherDepreciationAndAmortization.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Bridges to LBO!D13 LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="I8" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M employees</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>1,370</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Headcount in sales &amp; marketing.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>10-K Human Capital disclosure (3,180 total).</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Denominator for SDR % assumption.</t>
+        </is>
+      </c>
+      <c r="I9" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — ZI_02_SM_Isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_02_SM_Isolation` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Target mature SaaS S&amp;M % rev</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Benchmark efficient S&amp;M intensity.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input vs FY25 33.2%.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Defines “bloat” dollars vs a mature SaaS target.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>